--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="R109" t="n">
-        <v>2.79</v>
+        <v>3.73</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.74</v>
+        <v>2.08</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="R118" t="n">
-        <v>2.74</v>
+        <v>3.83</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G160" t="n">

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI160"/>
+  <dimension ref="A1:BI162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15720,27 +15720,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15908,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>46165.5625</v>
+        <v>46165.54166666666</v>
       </c>
     </row>
     <row r="79">
@@ -15917,27 +15917,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16105,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>46165.625</v>
+        <v>46165.54166666666</v>
       </c>
     </row>
     <row r="80">
@@ -16114,12 +16114,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16302,7 +16302,7 @@
         <v>0</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>46165.625</v>
+        <v>46165.5625</v>
       </c>
     </row>
     <row r="81">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16705,27 +16705,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16893,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>46165.63541666666</v>
+        <v>46165.625</v>
       </c>
     </row>
     <row r="84">
@@ -16902,12 +16902,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17090,7 +17090,7 @@
         <v>0</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>46165.64583333334</v>
+        <v>46165.625</v>
       </c>
     </row>
     <row r="85">
@@ -17099,27 +17099,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>46165.64583333334</v>
+        <v>46165.63541666666</v>
       </c>
     </row>
     <row r="86">
@@ -17296,27 +17296,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17484,7 +17484,7 @@
         <v>0</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>46165.65625</v>
+        <v>46165.64583333334</v>
       </c>
     </row>
     <row r="87">
@@ -17493,27 +17493,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17681,7 +17681,7 @@
         <v>0</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>46165.65625</v>
+        <v>46165.64583333334</v>
       </c>
     </row>
     <row r="88">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17887,27 +17887,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18075,7 +18075,7 @@
         <v>0</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>46165.66666666666</v>
+        <v>46165.65625</v>
       </c>
     </row>
     <row r="90">
@@ -18084,27 +18084,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18272,7 +18272,7 @@
         <v>0</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>46165.66666666666</v>
+        <v>46165.65625</v>
       </c>
     </row>
     <row r="91">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21039,12 +21039,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21227,7 +21227,7 @@
         <v>0</v>
       </c>
       <c r="BI105" s="3" t="n">
-        <v>46165.6875</v>
+        <v>46165.66666666666</v>
       </c>
     </row>
     <row r="106">
@@ -21236,12 +21236,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21424,7 +21424,7 @@
         <v>0</v>
       </c>
       <c r="BI106" s="3" t="n">
-        <v>46165.70833333334</v>
+        <v>46165.66666666666</v>
       </c>
     </row>
     <row r="107">
@@ -21433,12 +21433,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21621,7 +21621,7 @@
         <v>0</v>
       </c>
       <c r="BI107" s="3" t="n">
-        <v>46165.70833333334</v>
+        <v>46165.6875</v>
       </c>
     </row>
     <row r="108">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22024,12 +22024,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22212,7 +22212,7 @@
         <v>0</v>
       </c>
       <c r="BI110" s="3" t="n">
-        <v>46165.72916666666</v>
+        <v>46165.70833333334</v>
       </c>
     </row>
     <row r="111">
@@ -22221,12 +22221,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="BI111" s="3" t="n">
-        <v>46165.75</v>
+        <v>46165.70833333334</v>
       </c>
     </row>
     <row r="112">
@@ -22418,12 +22418,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22606,7 +22606,7 @@
         <v>0</v>
       </c>
       <c r="BI112" s="3" t="n">
-        <v>46165.76041666666</v>
+        <v>46165.72916666666</v>
       </c>
     </row>
     <row r="113">
@@ -22615,12 +22615,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22803,7 +22803,7 @@
         <v>0</v>
       </c>
       <c r="BI113" s="3" t="n">
-        <v>46165.77083333334</v>
+        <v>46165.75</v>
       </c>
     </row>
     <row r="114">
@@ -22812,12 +22812,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23000,7 +23000,7 @@
         <v>0</v>
       </c>
       <c r="BI114" s="3" t="n">
-        <v>46165.77083333334</v>
+        <v>46165.76041666666</v>
       </c>
     </row>
     <row r="115">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23206,12 +23206,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23394,7 +23394,7 @@
         <v>0</v>
       </c>
       <c r="BI116" s="3" t="n">
-        <v>46165.79166666666</v>
+        <v>46165.77083333334</v>
       </c>
     </row>
     <row r="117">
@@ -23403,12 +23403,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23591,7 +23591,7 @@
         <v>0</v>
       </c>
       <c r="BI117" s="3" t="n">
-        <v>46165.79166666666</v>
+        <v>46165.77083333334</v>
       </c>
     </row>
     <row r="118">
@@ -23994,12 +23994,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24182,7 +24182,7 @@
         <v>0</v>
       </c>
       <c r="BI120" s="3" t="n">
-        <v>46165.8125</v>
+        <v>46165.79166666666</v>
       </c>
     </row>
     <row r="121">
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24379,7 +24379,7 @@
         <v>0</v>
       </c>
       <c r="BI121" s="3" t="n">
-        <v>46165.8125</v>
+        <v>46165.79166666666</v>
       </c>
     </row>
     <row r="122">
@@ -24585,12 +24585,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24773,7 +24773,7 @@
         <v>0</v>
       </c>
       <c r="BI123" s="3" t="n">
-        <v>46165.83333333334</v>
+        <v>46165.8125</v>
       </c>
     </row>
     <row r="124">
@@ -24782,12 +24782,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24970,7 +24970,7 @@
         <v>0</v>
       </c>
       <c r="BI124" s="3" t="n">
-        <v>46165.83333333334</v>
+        <v>46165.8125</v>
       </c>
     </row>
     <row r="125">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25176,12 +25176,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25364,7 +25364,7 @@
         <v>0</v>
       </c>
       <c r="BI126" s="3" t="n">
-        <v>46165.85416666666</v>
+        <v>46165.83333333334</v>
       </c>
     </row>
     <row r="127">
@@ -25373,12 +25373,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25561,7 +25561,7 @@
         <v>0</v>
       </c>
       <c r="BI127" s="3" t="n">
-        <v>46165.85416666666</v>
+        <v>46165.83333333334</v>
       </c>
     </row>
     <row r="128">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26555,12 +26555,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26743,7 +26743,7 @@
         <v>0</v>
       </c>
       <c r="BI133" s="3" t="n">
-        <v>46165.875</v>
+        <v>46165.85416666666</v>
       </c>
     </row>
     <row r="134">
@@ -26752,27 +26752,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26940,7 +26940,7 @@
         <v>0</v>
       </c>
       <c r="BI134" s="3" t="n">
-        <v>46165.875</v>
+        <v>46165.85416666666</v>
       </c>
     </row>
     <row r="135">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29313,27 +29313,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29501,7 +29501,7 @@
         <v>0</v>
       </c>
       <c r="BI147" s="3" t="n">
-        <v>46165.89583333334</v>
+        <v>46165.875</v>
       </c>
     </row>
     <row r="148">
@@ -29510,27 +29510,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29698,7 +29698,7 @@
         <v>0</v>
       </c>
       <c r="BI148" s="3" t="n">
-        <v>46165.89583333334</v>
+        <v>46165.875</v>
       </c>
     </row>
     <row r="149">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30298,12 +30298,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30486,7 +30486,7 @@
         <v>0</v>
       </c>
       <c r="BI152" s="3" t="n">
-        <v>46165.90625</v>
+        <v>46165.89583333334</v>
       </c>
     </row>
     <row r="153">
@@ -30495,12 +30495,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30683,7 +30683,7 @@
         <v>0</v>
       </c>
       <c r="BI153" s="3" t="n">
-        <v>46165.91666666666</v>
+        <v>46165.89583333334</v>
       </c>
     </row>
     <row r="154">
@@ -30692,12 +30692,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30880,7 +30880,7 @@
         <v>0</v>
       </c>
       <c r="BI154" s="3" t="n">
-        <v>46165.9375</v>
+        <v>46165.90625</v>
       </c>
     </row>
     <row r="155">
@@ -30889,12 +30889,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31077,7 +31077,7 @@
         <v>0</v>
       </c>
       <c r="BI155" s="3" t="n">
-        <v>46165.9375</v>
+        <v>46165.91666666666</v>
       </c>
     </row>
     <row r="156">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31283,12 +31283,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31471,7 +31471,7 @@
         <v>0</v>
       </c>
       <c r="BI157" s="3" t="n">
-        <v>46165.95833333334</v>
+        <v>46165.9375</v>
       </c>
     </row>
     <row r="158">
@@ -31480,12 +31480,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31668,7 +31668,7 @@
         <v>0</v>
       </c>
       <c r="BI158" s="3" t="n">
-        <v>46165.95833333334</v>
+        <v>46165.9375</v>
       </c>
     </row>
     <row r="159">
@@ -31677,12 +31677,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31865,7 +31865,7 @@
         <v>0</v>
       </c>
       <c r="BI159" s="3" t="n">
-        <v>46165.97916666666</v>
+        <v>46165.95833333334</v>
       </c>
     </row>
     <row r="160">
@@ -31874,7 +31874,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32062,6 +32062,400 @@
         <v>0</v>
       </c>
       <c r="BI160" s="3" t="n">
+        <v>46165.95833333334</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Colorado Springs</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
+        <v>0</v>
+      </c>
+      <c r="U161" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" t="n">
+        <v>0</v>
+      </c>
+      <c r="W161" t="n">
+        <v>0</v>
+      </c>
+      <c r="X161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI161" s="3" t="n">
+        <v>46165.97916666666</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="n">
+        <v>0</v>
+      </c>
+      <c r="V162" t="n">
+        <v>0</v>
+      </c>
+      <c r="W162" t="n">
+        <v>0</v>
+      </c>
+      <c r="X162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI162" s="3" t="n">
         <v>46165.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI162"/>
+  <dimension ref="A1:BI163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15720,12 +15720,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15908,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>46165.54166666666</v>
+        <v>46165.52083333334</v>
       </c>
     </row>
     <row r="79">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16114,27 +16114,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16302,7 +16302,7 @@
         <v>0</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>46165.5625</v>
+        <v>46165.54166666666</v>
       </c>
     </row>
     <row r="81">
@@ -16311,12 +16311,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16499,7 +16499,7 @@
         <v>0</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>46165.625</v>
+        <v>46165.5625</v>
       </c>
     </row>
     <row r="82">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17099,27 +17099,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>46165.63541666666</v>
+        <v>46165.625</v>
       </c>
     </row>
     <row r="86">
@@ -17296,27 +17296,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17484,7 +17484,7 @@
         <v>0</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>46165.64583333334</v>
+        <v>46165.63541666666</v>
       </c>
     </row>
     <row r="87">
@@ -17690,27 +17690,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17878,7 +17878,7 @@
         <v>0</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>46165.65625</v>
+        <v>46165.64583333334</v>
       </c>
     </row>
     <row r="89">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18281,12 +18281,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>46165.66666666666</v>
+        <v>46165.65625</v>
       </c>
     </row>
     <row r="92">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21433,27 +21433,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21621,7 +21621,7 @@
         <v>0</v>
       </c>
       <c r="BI107" s="3" t="n">
-        <v>46165.6875</v>
+        <v>46165.66666666666</v>
       </c>
     </row>
     <row r="108">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21818,7 +21818,7 @@
         <v>0</v>
       </c>
       <c r="BI108" s="3" t="n">
-        <v>46165.70833333334</v>
+        <v>46165.6875</v>
       </c>
     </row>
     <row r="109">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="R110" t="n">
-        <v>2.79</v>
+        <v>3.73</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22418,12 +22418,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22606,7 +22606,7 @@
         <v>0</v>
       </c>
       <c r="BI112" s="3" t="n">
-        <v>46165.72916666666</v>
+        <v>46165.70833333334</v>
       </c>
     </row>
     <row r="113">
@@ -22615,12 +22615,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22803,7 +22803,7 @@
         <v>0</v>
       </c>
       <c r="BI113" s="3" t="n">
-        <v>46165.75</v>
+        <v>46165.72916666666</v>
       </c>
     </row>
     <row r="114">
@@ -22812,12 +22812,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23000,7 +23000,7 @@
         <v>0</v>
       </c>
       <c r="BI114" s="3" t="n">
-        <v>46165.76041666666</v>
+        <v>46165.75</v>
       </c>
     </row>
     <row r="115">
@@ -23009,12 +23009,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23197,7 +23197,7 @@
         <v>0</v>
       </c>
       <c r="BI115" s="3" t="n">
-        <v>46165.77083333334</v>
+        <v>46165.76041666666</v>
       </c>
     </row>
     <row r="116">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23788,7 +23788,7 @@
         <v>0</v>
       </c>
       <c r="BI118" s="3" t="n">
-        <v>46165.79166666666</v>
+        <v>46165.77083333334</v>
       </c>
     </row>
     <row r="119">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24388,12 +24388,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24576,7 +24576,7 @@
         <v>0</v>
       </c>
       <c r="BI122" s="3" t="n">
-        <v>46165.8125</v>
+        <v>46165.79166666666</v>
       </c>
     </row>
     <row r="123">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24979,12 +24979,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25167,7 +25167,7 @@
         <v>0</v>
       </c>
       <c r="BI125" s="3" t="n">
-        <v>46165.83333333334</v>
+        <v>46165.8125</v>
       </c>
     </row>
     <row r="126">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25570,12 +25570,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25758,7 +25758,7 @@
         <v>0</v>
       </c>
       <c r="BI128" s="3" t="n">
-        <v>46165.85416666666</v>
+        <v>46165.83333333334</v>
       </c>
     </row>
     <row r="129">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26949,12 +26949,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27137,7 +27137,7 @@
         <v>0</v>
       </c>
       <c r="BI135" s="3" t="n">
-        <v>46165.875</v>
+        <v>46165.85416666666</v>
       </c>
     </row>
     <row r="136">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29707,27 +29707,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29895,7 +29895,7 @@
         <v>0</v>
       </c>
       <c r="BI149" s="3" t="n">
-        <v>46165.89583333334</v>
+        <v>46165.875</v>
       </c>
     </row>
     <row r="150">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30692,12 +30692,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30880,7 +30880,7 @@
         <v>0</v>
       </c>
       <c r="BI154" s="3" t="n">
-        <v>46165.90625</v>
+        <v>46165.89583333334</v>
       </c>
     </row>
     <row r="155">
@@ -30889,12 +30889,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31077,7 +31077,7 @@
         <v>0</v>
       </c>
       <c r="BI155" s="3" t="n">
-        <v>46165.91666666666</v>
+        <v>46165.90625</v>
       </c>
     </row>
     <row r="156">
@@ -31086,12 +31086,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31274,7 +31274,7 @@
         <v>0</v>
       </c>
       <c r="BI156" s="3" t="n">
-        <v>46165.9375</v>
+        <v>46165.91666666666</v>
       </c>
     </row>
     <row r="157">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31677,12 +31677,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31865,7 +31865,7 @@
         <v>0</v>
       </c>
       <c r="BI159" s="3" t="n">
-        <v>46165.95833333334</v>
+        <v>46165.9375</v>
       </c>
     </row>
     <row r="160">
@@ -32071,7 +32071,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32259,7 +32259,7 @@
         <v>0</v>
       </c>
       <c r="BI161" s="3" t="n">
-        <v>46165.97916666666</v>
+        <v>46165.95833333334</v>
       </c>
     </row>
     <row r="162">
@@ -32456,6 +32456,203 @@
         <v>0</v>
       </c>
       <c r="BI162" s="3" t="n">
+        <v>46165.97916666666</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Colorado Springs</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="n">
+        <v>0</v>
+      </c>
+      <c r="V163" t="n">
+        <v>0</v>
+      </c>
+      <c r="W163" t="n">
+        <v>0</v>
+      </c>
+      <c r="X163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI163" s="3" t="n">
         <v>46165.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="R122" t="n">
-        <v>3.83</v>
+        <v>2.74</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G163" t="n">

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G163" t="n">

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>16.3</v>
+        <v>1.56</v>
       </c>
       <c r="Q45" t="n">
-        <v>7.39</v>
+        <v>3.67</v>
       </c>
       <c r="R45" t="n">
-        <v>1.12</v>
+        <v>5.75</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="R48" t="n">
-        <v>2.65</v>
+        <v>3.63</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.67</v>
+        <v>3.35</v>
       </c>
       <c r="R50" t="n">
-        <v>5.75</v>
+        <v>3.23</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="R53" t="n">
-        <v>3.39</v>
+        <v>2.65</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.35</v>
+        <v>3.07</v>
       </c>
       <c r="R57" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="R112" t="n">
-        <v>2.79</v>
+        <v>3.73</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G158" t="n">

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>16.3</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.38</v>
+        <v>3.08</v>
       </c>
       <c r="R47" t="n">
-        <v>2.83</v>
+        <v>3.39</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="R50" t="n">
-        <v>3.23</v>
+        <v>2.65</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.38</v>
+        <v>16.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.45</v>
+        <v>7.39</v>
       </c>
       <c r="R53" t="n">
-        <v>2.65</v>
+        <v>1.12</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.27</v>
+        <v>4.25</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="R70" t="n">
-        <v>3.2</v>
+        <v>1.82</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="Q73" t="n">
         <v>3.8</v>
       </c>
       <c r="R73" t="n">
-        <v>3.19</v>
+        <v>2.16</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>4.25</v>
+        <v>1.69</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.36</v>
+        <v>3.9</v>
       </c>
       <c r="R76" t="n">
-        <v>1.82</v>
+        <v>4.73</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="R111" t="n">
-        <v>2.79</v>
+        <v>3.73</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="R112" t="n">
-        <v>3.73</v>
+        <v>2.79</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G163" t="n">

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.38</v>
+        <v>16.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.45</v>
+        <v>7.39</v>
       </c>
       <c r="R50" t="n">
-        <v>2.65</v>
+        <v>1.12</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>16.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q53" t="n">
-        <v>7.39</v>
+        <v>3.45</v>
       </c>
       <c r="R53" t="n">
-        <v>1.12</v>
+        <v>2.65</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.56</v>
+        <v>2.34</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.67</v>
+        <v>3.38</v>
       </c>
       <c r="R54" t="n">
-        <v>5.75</v>
+        <v>2.83</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.35</v>
+        <v>2.93</v>
       </c>
       <c r="R55" t="n">
-        <v>3.23</v>
+        <v>3.59</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="R57" t="n">
-        <v>3.21</v>
+        <v>3.63</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>4.25</v>
+        <v>2.07</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="R70" t="n">
-        <v>1.82</v>
+        <v>3.19</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R72" t="n">
-        <v>5.38</v>
+        <v>2.16</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3</v>
+        <v>1.69</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R73" t="n">
-        <v>2.16</v>
+        <v>4.73</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R74" t="n">
-        <v>3.19</v>
+        <v>4.16</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.69</v>
+        <v>4.25</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.9</v>
+        <v>3.36</v>
       </c>
       <c r="R76" t="n">
-        <v>4.73</v>
+        <v>1.82</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.74</v>
+        <v>2.08</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="R122" t="n">
-        <v>2.74</v>
+        <v>3.83</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G163" t="n">

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.11</v>
+        <v>1.56</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.35</v>
+        <v>3.67</v>
       </c>
       <c r="R45" t="n">
-        <v>3.23</v>
+        <v>5.75</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>16.3</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.38</v>
+        <v>16.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.45</v>
+        <v>7.39</v>
       </c>
       <c r="R53" t="n">
-        <v>2.65</v>
+        <v>1.12</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11245,10 +11245,10 @@
         <v>2.19</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="R55" t="n">
-        <v>3.59</v>
+        <v>3.39</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.56</v>
+        <v>2.34</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.67</v>
+        <v>3.38</v>
       </c>
       <c r="R56" t="n">
-        <v>5.75</v>
+        <v>2.83</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="Q69" t="n">
         <v>3.9</v>
       </c>
       <c r="R69" t="n">
-        <v>5.38</v>
+        <v>4.16</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="Q72" t="n">
         <v>3.8</v>
       </c>
       <c r="R72" t="n">
-        <v>2.16</v>
+        <v>3.19</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>4.25</v>
+        <v>1.62</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.36</v>
+        <v>3.9</v>
       </c>
       <c r="R76" t="n">
-        <v>1.82</v>
+        <v>5.38</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G154" t="n">

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.56</v>
+        <v>2.34</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.67</v>
+        <v>3.38</v>
       </c>
       <c r="R45" t="n">
-        <v>5.75</v>
+        <v>2.83</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="R49" t="n">
-        <v>2.65</v>
+        <v>3.39</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.07</v>
+        <v>3.35</v>
       </c>
       <c r="R51" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.93</v>
+        <v>3.45</v>
       </c>
       <c r="R52" t="n">
-        <v>3.59</v>
+        <v>2.65</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.19</v>
+        <v>1.56</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.08</v>
+        <v>3.67</v>
       </c>
       <c r="R55" t="n">
-        <v>3.39</v>
+        <v>5.75</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.27</v>
+        <v>1.77</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="R68" t="n">
-        <v>3.2</v>
+        <v>4.16</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="R69" t="n">
-        <v>4.16</v>
+        <v>5</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.69</v>
+        <v>2.07</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R73" t="n">
-        <v>4.73</v>
+        <v>3.19</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.62</v>
+        <v>2.14</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>5.38</v>
+        <v>3.49</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R77" t="n">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="R78" t="n">
-        <v>1.82</v>
+        <v>2.16</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="R109" t="n">
-        <v>2.79</v>
+        <v>3.73</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="R111" t="n">
-        <v>3.73</v>
+        <v>2.79</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF113" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>2.74</v>
+        <v>2.08</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="R119" t="n">
-        <v>2.74</v>
+        <v>3.83</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="R121" t="n">
-        <v>3.83</v>
+        <v>2.74</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF130" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26259,10 +26259,10 @@
         <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF131" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG131" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF134" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27053,10 +27053,10 @@
         <v>0</v>
       </c>
       <c r="AG135" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH135" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI135" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30008,10 +30008,10 @@
         <v>0</v>
       </c>
       <c r="AG150" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH150" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30796,10 +30796,10 @@
         <v>0</v>
       </c>
       <c r="AG154" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH154" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI154" t="n">
         <v>0</v>
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31387,10 +31387,10 @@
         <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH157" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31584,10 +31584,10 @@
         <v>0</v>
       </c>
       <c r="AG158" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH158" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI158" t="n">
         <v>0</v>
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF160" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF161" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32563,10 +32563,10 @@
         <v>0</v>
       </c>
       <c r="AE163" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF163" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG163" t="n">
         <v>0</v>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI163"/>
+  <dimension ref="A1:BI167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46165.25</v>
+        <v>46165.21527777778</v>
       </c>
     </row>
     <row r="8">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3112,27 +3112,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46165.26041666666</v>
+        <v>46165.25</v>
       </c>
     </row>
     <row r="15">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46165.29166666666</v>
+        <v>46165.26041666666</v>
       </c>
     </row>
     <row r="16">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46165.33333333334</v>
+        <v>46165.29166666666</v>
       </c>
     </row>
     <row r="17">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46165.34375</v>
+        <v>46165.33333333334</v>
       </c>
     </row>
     <row r="26">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46165.35416666666</v>
+        <v>46165.34375</v>
       </c>
     </row>
     <row r="27">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46165.35763888889</v>
+        <v>46165.35416666666</v>
       </c>
     </row>
     <row r="29">
@@ -6067,27 +6067,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46165.375</v>
+        <v>46165.35763888889</v>
       </c>
     </row>
     <row r="30">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46165.41666666666</v>
+        <v>46165.375</v>
       </c>
     </row>
     <row r="45">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.34</v>
+        <v>16.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.38</v>
+        <v>7.39</v>
       </c>
       <c r="R45" t="n">
-        <v>2.83</v>
+        <v>1.12</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="R46" t="n">
-        <v>3.59</v>
+        <v>2.83</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.11</v>
+        <v>1.56</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.35</v>
+        <v>3.67</v>
       </c>
       <c r="R51" t="n">
-        <v>3.23</v>
+        <v>5.75</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>16.3</v>
+        <v>2.11</v>
       </c>
       <c r="Q53" t="n">
-        <v>7.39</v>
+        <v>3.35</v>
       </c>
       <c r="R53" t="n">
-        <v>1.12</v>
+        <v>3.23</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="R54" t="n">
-        <v>3.63</v>
+        <v>2.65</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.56</v>
+        <v>2.16</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.67</v>
+        <v>2.95</v>
       </c>
       <c r="R55" t="n">
-        <v>5.75</v>
+        <v>3.63</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11780,27 +11780,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46165.45833333334</v>
+        <v>46165.41666666666</v>
       </c>
     </row>
     <row r="59">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
-        <v>46165.5</v>
+        <v>46165.45833333334</v>
       </c>
     </row>
     <row r="60">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12371,27 +12371,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46165.51736111111</v>
+        <v>46165.5</v>
       </c>
     </row>
     <row r="62">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13750,12 +13750,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13938,7 +13938,7 @@
         <v>0</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>46165.52083333334</v>
+        <v>46165.51736111111</v>
       </c>
     </row>
     <row r="69">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R73" t="n">
-        <v>3.19</v>
+        <v>5.38</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>4.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="R74" t="n">
-        <v>1.82</v>
+        <v>3.49</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="Q75" t="n">
         <v>3.9</v>
       </c>
       <c r="R75" t="n">
-        <v>5.38</v>
+        <v>4.73</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="Q76" t="n">
         <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>3.49</v>
+        <v>3.2</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.27</v>
+        <v>4.25</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="R77" t="n">
-        <v>3.2</v>
+        <v>1.82</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="Q78" t="n">
         <v>3.8</v>
       </c>
       <c r="R78" t="n">
-        <v>2.16</v>
+        <v>3.19</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15917,12 +15917,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16105,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>46165.54166666666</v>
+        <v>46165.52083333334</v>
       </c>
     </row>
     <row r="80">
@@ -16114,12 +16114,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16302,7 +16302,7 @@
         <v>0</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>46165.54166666666</v>
+        <v>46165.52083333334</v>
       </c>
     </row>
     <row r="81">
@@ -16311,27 +16311,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16499,7 +16499,7 @@
         <v>0</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>46165.5625</v>
+        <v>46165.52083333334</v>
       </c>
     </row>
     <row r="82">
@@ -16508,27 +16508,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16696,7 +16696,7 @@
         <v>0</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>46165.625</v>
+        <v>46165.54166666666</v>
       </c>
     </row>
     <row r="83">
@@ -16705,27 +16705,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16893,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>46165.625</v>
+        <v>46165.54166666666</v>
       </c>
     </row>
     <row r="84">
@@ -16902,12 +16902,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17090,7 +17090,7 @@
         <v>0</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>46165.625</v>
+        <v>46165.5625</v>
       </c>
     </row>
     <row r="85">
@@ -17296,27 +17296,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17484,7 +17484,7 @@
         <v>0</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>46165.63541666666</v>
+        <v>46165.625</v>
       </c>
     </row>
     <row r="87">
@@ -17493,7 +17493,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17681,7 +17681,7 @@
         <v>0</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>46165.64583333334</v>
+        <v>46165.625</v>
       </c>
     </row>
     <row r="88">
@@ -17690,12 +17690,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
         <v>0</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>46165.64583333334</v>
+        <v>46165.625</v>
       </c>
     </row>
     <row r="89">
@@ -17887,12 +17887,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18075,7 +18075,7 @@
         <v>0</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>46165.65625</v>
+        <v>46165.63541666666</v>
       </c>
     </row>
     <row r="90">
@@ -18084,27 +18084,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18272,7 +18272,7 @@
         <v>0</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>46165.65625</v>
+        <v>46165.64583333334</v>
       </c>
     </row>
     <row r="91">
@@ -18281,27 +18281,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.74</v>
+        <v>1.58</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.46</v>
+        <v>4.05</v>
       </c>
       <c r="R91" t="n">
-        <v>2.54</v>
+        <v>4.65</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>46165.65625</v>
+        <v>46165.64583333334</v>
       </c>
     </row>
     <row r="92">
@@ -18478,27 +18478,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18666,7 +18666,7 @@
         <v>0</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>46165.66666666666</v>
+        <v>46165.65625</v>
       </c>
     </row>
     <row r="93">
@@ -18675,12 +18675,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18863,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>46165.66666666666</v>
+        <v>46165.65625</v>
       </c>
     </row>
     <row r="94">
@@ -18872,12 +18872,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19060,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46165.66666666666</v>
+        <v>46165.65625</v>
       </c>
     </row>
     <row r="95">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21630,27 +21630,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21818,7 +21818,7 @@
         <v>0</v>
       </c>
       <c r="BI108" s="3" t="n">
-        <v>46165.6875</v>
+        <v>46165.66666666666</v>
       </c>
     </row>
     <row r="109">
@@ -21827,12 +21827,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22015,7 +22015,7 @@
         <v>0</v>
       </c>
       <c r="BI109" s="3" t="n">
-        <v>46165.70833333334</v>
+        <v>46165.66666666666</v>
       </c>
     </row>
     <row r="110">
@@ -22024,12 +22024,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22212,7 +22212,7 @@
         <v>0</v>
       </c>
       <c r="BI110" s="3" t="n">
-        <v>46165.70833333334</v>
+        <v>46165.66666666666</v>
       </c>
     </row>
     <row r="111">
@@ -22221,12 +22221,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="BI111" s="3" t="n">
-        <v>46165.70833333334</v>
+        <v>46165.6875</v>
       </c>
     </row>
     <row r="112">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22615,12 +22615,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="R113" t="n">
-        <v>3.17</v>
+        <v>2.79</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF113" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22803,7 +22803,7 @@
         <v>0</v>
       </c>
       <c r="BI113" s="3" t="n">
-        <v>46165.72916666666</v>
+        <v>46165.70833333334</v>
       </c>
     </row>
     <row r="114">
@@ -22812,12 +22812,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23000,7 +23000,7 @@
         <v>0</v>
       </c>
       <c r="BI114" s="3" t="n">
-        <v>46165.75</v>
+        <v>46165.70833333334</v>
       </c>
     </row>
     <row r="115">
@@ -23009,12 +23009,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23197,7 +23197,7 @@
         <v>0</v>
       </c>
       <c r="BI115" s="3" t="n">
-        <v>46165.76041666666</v>
+        <v>46165.70833333334</v>
       </c>
     </row>
     <row r="116">
@@ -23206,12 +23206,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF116" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23394,7 +23394,7 @@
         <v>0</v>
       </c>
       <c r="BI116" s="3" t="n">
-        <v>46165.77083333334</v>
+        <v>46165.72916666666</v>
       </c>
     </row>
     <row r="117">
@@ -23403,12 +23403,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23591,7 +23591,7 @@
         <v>0</v>
       </c>
       <c r="BI117" s="3" t="n">
-        <v>46165.77083333334</v>
+        <v>46165.75</v>
       </c>
     </row>
     <row r="118">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23788,7 +23788,7 @@
         <v>0</v>
       </c>
       <c r="BI118" s="3" t="n">
-        <v>46165.77083333334</v>
+        <v>46165.76041666666</v>
       </c>
     </row>
     <row r="119">
@@ -23797,12 +23797,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="BI119" s="3" t="n">
-        <v>46165.79166666666</v>
+        <v>46165.77083333334</v>
       </c>
     </row>
     <row r="120">
@@ -23994,12 +23994,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24182,7 +24182,7 @@
         <v>0</v>
       </c>
       <c r="BI120" s="3" t="n">
-        <v>46165.79166666666</v>
+        <v>46165.77083333334</v>
       </c>
     </row>
     <row r="121">
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24379,7 +24379,7 @@
         <v>0</v>
       </c>
       <c r="BI121" s="3" t="n">
-        <v>46165.79166666666</v>
+        <v>46165.77083333334</v>
       </c>
     </row>
     <row r="122">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24585,12 +24585,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24773,7 +24773,7 @@
         <v>0</v>
       </c>
       <c r="BI123" s="3" t="n">
-        <v>46165.8125</v>
+        <v>46165.79166666666</v>
       </c>
     </row>
     <row r="124">
@@ -24782,12 +24782,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24970,7 +24970,7 @@
         <v>0</v>
       </c>
       <c r="BI124" s="3" t="n">
-        <v>46165.8125</v>
+        <v>46165.79166666666</v>
       </c>
     </row>
     <row r="125">
@@ -24979,12 +24979,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25167,7 +25167,7 @@
         <v>0</v>
       </c>
       <c r="BI125" s="3" t="n">
-        <v>46165.8125</v>
+        <v>46165.79166666666</v>
       </c>
     </row>
     <row r="126">
@@ -25176,12 +25176,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF126" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25364,7 +25364,7 @@
         <v>0</v>
       </c>
       <c r="BI126" s="3" t="n">
-        <v>46165.83333333334</v>
+        <v>46165.8125</v>
       </c>
     </row>
     <row r="127">
@@ -25373,12 +25373,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25561,7 +25561,7 @@
         <v>0</v>
       </c>
       <c r="BI127" s="3" t="n">
-        <v>46165.83333333334</v>
+        <v>46165.8125</v>
       </c>
     </row>
     <row r="128">
@@ -25570,12 +25570,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25758,7 +25758,7 @@
         <v>0</v>
       </c>
       <c r="BI128" s="3" t="n">
-        <v>46165.83333333334</v>
+        <v>46165.8125</v>
       </c>
     </row>
     <row r="129">
@@ -25767,12 +25767,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25955,7 +25955,7 @@
         <v>0</v>
       </c>
       <c r="BI129" s="3" t="n">
-        <v>46165.85416666666</v>
+        <v>46165.83333333334</v>
       </c>
     </row>
     <row r="130">
@@ -25964,12 +25964,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R130" t="n">
-        <v>3.58</v>
+        <v>2.75</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26065,7 +26065,7 @@
         <v>1.79</v>
       </c>
       <c r="AF130" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26152,7 +26152,7 @@
         <v>0</v>
       </c>
       <c r="BI130" s="3" t="n">
-        <v>46165.85416666666</v>
+        <v>46165.83333333334</v>
       </c>
     </row>
     <row r="131">
@@ -26161,7 +26161,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26259,10 +26259,10 @@
         <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF131" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG131" t="n">
         <v>0</v>
@@ -26349,7 +26349,7 @@
         <v>0</v>
       </c>
       <c r="BI131" s="3" t="n">
-        <v>46165.85416666666</v>
+        <v>46165.83333333334</v>
       </c>
     </row>
     <row r="132">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.89</v>
+        <v>4.78</v>
       </c>
       <c r="R134" t="n">
-        <v>4.08</v>
+        <v>4.78</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,16 +26850,16 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF134" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG134" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH134" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI134" t="n">
         <v>0</v>
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="Q135" t="n">
-        <v>4.78</v>
+        <v>3.8</v>
       </c>
       <c r="R135" t="n">
-        <v>4.78</v>
+        <v>3.58</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,16 +27047,16 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF135" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG135" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH135" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI135" t="n">
         <v>0</v>
@@ -27146,27 +27146,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF136" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27334,7 +27334,7 @@
         <v>0</v>
       </c>
       <c r="BI136" s="3" t="n">
-        <v>46165.875</v>
+        <v>46165.85416666666</v>
       </c>
     </row>
     <row r="137">
@@ -27343,27 +27343,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27531,7 +27531,7 @@
         <v>0</v>
       </c>
       <c r="BI137" s="3" t="n">
-        <v>46165.875</v>
+        <v>46165.85416666666</v>
       </c>
     </row>
     <row r="138">
@@ -27540,12 +27540,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>3.01</v>
+        <v>1.89</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.2</v>
+        <v>3.89</v>
       </c>
       <c r="R138" t="n">
-        <v>2.36</v>
+        <v>4.08</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27728,7 +27728,7 @@
         <v>0</v>
       </c>
       <c r="BI138" s="3" t="n">
-        <v>46165.875</v>
+        <v>46165.85416666666</v>
       </c>
     </row>
     <row r="139">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29904,27 +29904,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30008,10 +30008,10 @@
         <v>0</v>
       </c>
       <c r="AG150" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH150" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI150" t="n">
         <v>0</v>
@@ -30092,7 +30092,7 @@
         <v>0</v>
       </c>
       <c r="BI150" s="3" t="n">
-        <v>46165.89583333334</v>
+        <v>46165.875</v>
       </c>
     </row>
     <row r="151">
@@ -30101,27 +30101,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30289,7 +30289,7 @@
         <v>0</v>
       </c>
       <c r="BI151" s="3" t="n">
-        <v>46165.89583333334</v>
+        <v>46165.875</v>
       </c>
     </row>
     <row r="152">
@@ -30298,27 +30298,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30486,7 +30486,7 @@
         <v>0</v>
       </c>
       <c r="BI152" s="3" t="n">
-        <v>46165.89583333334</v>
+        <v>46165.875</v>
       </c>
     </row>
     <row r="153">
@@ -30495,12 +30495,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30683,7 +30683,7 @@
         <v>0</v>
       </c>
       <c r="BI153" s="3" t="n">
-        <v>46165.89583333334</v>
+        <v>46165.875</v>
       </c>
     </row>
     <row r="154">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>3.08</v>
+        <v>2.42</v>
       </c>
       <c r="Q154" t="n">
-        <v>4.26</v>
+        <v>3</v>
       </c>
       <c r="R154" t="n">
-        <v>2.12</v>
+        <v>3.03</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30796,10 +30796,10 @@
         <v>0</v>
       </c>
       <c r="AG154" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH154" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI154" t="n">
         <v>0</v>
@@ -30889,12 +30889,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30993,10 +30993,10 @@
         <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH155" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31077,7 +31077,7 @@
         <v>0</v>
       </c>
       <c r="BI155" s="3" t="n">
-        <v>46165.90625</v>
+        <v>46165.89583333334</v>
       </c>
     </row>
     <row r="156">
@@ -31086,12 +31086,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31274,7 +31274,7 @@
         <v>0</v>
       </c>
       <c r="BI156" s="3" t="n">
-        <v>46165.91666666666</v>
+        <v>46165.89583333334</v>
       </c>
     </row>
     <row r="157">
@@ -31283,12 +31283,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31387,10 +31387,10 @@
         <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH157" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
@@ -31471,7 +31471,7 @@
         <v>0</v>
       </c>
       <c r="BI157" s="3" t="n">
-        <v>46165.9375</v>
+        <v>46165.89583333334</v>
       </c>
     </row>
     <row r="158">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>3.9</v>
+        <v>3.08</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.95</v>
+        <v>4.26</v>
       </c>
       <c r="R158" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31584,10 +31584,10 @@
         <v>0</v>
       </c>
       <c r="AG158" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AH158" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="AI158" t="n">
         <v>0</v>
@@ -31668,7 +31668,7 @@
         <v>0</v>
       </c>
       <c r="BI158" s="3" t="n">
-        <v>46165.9375</v>
+        <v>46165.89583333334</v>
       </c>
     </row>
     <row r="159">
@@ -31677,12 +31677,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31865,7 +31865,7 @@
         <v>0</v>
       </c>
       <c r="BI159" s="3" t="n">
-        <v>46165.9375</v>
+        <v>46165.90625</v>
       </c>
     </row>
     <row r="160">
@@ -31874,7 +31874,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF160" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32062,7 +32062,7 @@
         <v>0</v>
       </c>
       <c r="BI160" s="3" t="n">
-        <v>46165.95833333334</v>
+        <v>46165.91666666666</v>
       </c>
     </row>
     <row r="161">
@@ -32071,12 +32071,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="R161" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,16 +32169,16 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF161" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG161" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH161" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI161" t="n">
         <v>0</v>
@@ -32259,7 +32259,7 @@
         <v>0</v>
       </c>
       <c r="BI161" s="3" t="n">
-        <v>46165.95833333334</v>
+        <v>46165.9375</v>
       </c>
     </row>
     <row r="162">
@@ -32268,12 +32268,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="R162" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32372,10 +32372,10 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH162" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -32456,7 +32456,7 @@
         <v>0</v>
       </c>
       <c r="BI162" s="3" t="n">
-        <v>46165.97916666666</v>
+        <v>46165.9375</v>
       </c>
     </row>
     <row r="163">
@@ -32465,7 +32465,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,141 +32518,929 @@
         </is>
       </c>
       <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="n">
+        <v>0</v>
+      </c>
+      <c r="V163" t="n">
+        <v>0</v>
+      </c>
+      <c r="W163" t="n">
+        <v>0</v>
+      </c>
+      <c r="X163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI163" s="3" t="n">
+        <v>46165.9375</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R164" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
+        <v>0</v>
+      </c>
+      <c r="U164" t="n">
+        <v>0</v>
+      </c>
+      <c r="V164" t="n">
+        <v>0</v>
+      </c>
+      <c r="W164" t="n">
+        <v>0</v>
+      </c>
+      <c r="X164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI164" s="3" t="n">
+        <v>46165.95833333334</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Birmingham Legion</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R165" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S165" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" t="n">
+        <v>0</v>
+      </c>
+      <c r="U165" t="n">
+        <v>0</v>
+      </c>
+      <c r="V165" t="n">
+        <v>0</v>
+      </c>
+      <c r="W165" t="n">
+        <v>0</v>
+      </c>
+      <c r="X165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI165" s="3" t="n">
+        <v>46165.95833333334</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q163" t="n">
+      <c r="Q166" t="n">
         <v>3.6</v>
       </c>
-      <c r="R163" t="n">
+      <c r="R166" t="n">
         <v>3.45</v>
       </c>
-      <c r="S163" t="n">
-        <v>0</v>
-      </c>
-      <c r="T163" t="n">
-        <v>0</v>
-      </c>
-      <c r="U163" t="n">
-        <v>0</v>
-      </c>
-      <c r="V163" t="n">
-        <v>0</v>
-      </c>
-      <c r="W163" t="n">
-        <v>0</v>
-      </c>
-      <c r="X163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE163" t="n">
+      <c r="S166" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" t="n">
+        <v>0</v>
+      </c>
+      <c r="V166" t="n">
+        <v>0</v>
+      </c>
+      <c r="W166" t="n">
+        <v>0</v>
+      </c>
+      <c r="X166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="n">
         <v>1.57</v>
       </c>
-      <c r="AF163" t="n">
+      <c r="AF166" t="n">
         <v>2.25</v>
       </c>
-      <c r="AG163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI163" s="3" t="n">
+      <c r="AG166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI166" s="3" t="n">
+        <v>46165.97916666666</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Colorado Springs</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R167" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="n">
+        <v>0</v>
+      </c>
+      <c r="V167" t="n">
+        <v>0</v>
+      </c>
+      <c r="W167" t="n">
+        <v>0</v>
+      </c>
+      <c r="X167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI167" s="3" t="n">
         <v>46165.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>16.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q45" t="n">
-        <v>7.39</v>
+        <v>2.93</v>
       </c>
       <c r="R45" t="n">
-        <v>1.12</v>
+        <v>3.59</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10260,10 +10260,10 @@
         <v>2.19</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="R50" t="n">
-        <v>3.59</v>
+        <v>3.39</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.56</v>
+        <v>2.16</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.67</v>
+        <v>2.95</v>
       </c>
       <c r="R51" t="n">
-        <v>5.75</v>
+        <v>3.63</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R54" t="n">
-        <v>2.65</v>
+        <v>3.23</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.95</v>
+        <v>3.38</v>
       </c>
       <c r="R55" t="n">
-        <v>3.63</v>
+        <v>2.83</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.19</v>
+        <v>16.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.08</v>
+        <v>7.39</v>
       </c>
       <c r="R58" t="n">
-        <v>3.39</v>
+        <v>1.12</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="R70" t="n">
-        <v>6.36</v>
+        <v>5.38</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="R72" t="n">
-        <v>2.16</v>
+        <v>5</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.62</v>
+        <v>2.14</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R73" t="n">
-        <v>5.38</v>
+        <v>3.49</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="Q74" t="n">
         <v>3.3</v>
       </c>
       <c r="R74" t="n">
-        <v>3.49</v>
+        <v>3.2</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.27</v>
+        <v>4.25</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="R76" t="n">
-        <v>3.2</v>
+        <v>1.82</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="R79" t="n">
-        <v>5</v>
+        <v>6.36</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="Q80" t="n">
         <v>3.9</v>
       </c>
       <c r="R80" t="n">
-        <v>4.16</v>
+        <v>4.73</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.46</v>
+        <v>3.71</v>
       </c>
       <c r="R92" t="n">
-        <v>2.54</v>
+        <v>2.94</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.29</v>
+        <v>2.74</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.71</v>
+        <v>3.46</v>
       </c>
       <c r="R94" t="n">
-        <v>2.94</v>
+        <v>2.54</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="R115" t="n">
-        <v>3.73</v>
+        <v>2.79</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.74</v>
+        <v>2.08</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="R122" t="n">
-        <v>2.74</v>
+        <v>3.83</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF132" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="R136" t="n">
-        <v>4.68</v>
+        <v>4.08</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AF136" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,22 +30500,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>1.6</v>
+        <v>3.08</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.58</v>
+        <v>4.26</v>
       </c>
       <c r="R155" t="n">
-        <v>5.3</v>
+        <v>2.12</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30993,10 +30993,10 @@
         <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>3.08</v>
+        <v>1.6</v>
       </c>
       <c r="Q158" t="n">
-        <v>4.26</v>
+        <v>4.58</v>
       </c>
       <c r="R158" t="n">
-        <v>2.12</v>
+        <v>5.3</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31584,10 +31584,10 @@
         <v>0</v>
       </c>
       <c r="AG158" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AH158" t="n">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="AI158" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>1.92</v>
+        <v>3.3</v>
       </c>
       <c r="Q166" t="n">
         <v>3.6</v>
       </c>
       <c r="R166" t="n">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33154,10 +33154,10 @@
         <v>0</v>
       </c>
       <c r="AE166" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF166" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>3.3</v>
+        <v>1.92</v>
       </c>
       <c r="Q167" t="n">
         <v>3.6</v>
       </c>
       <c r="R167" t="n">
-        <v>1.9</v>
+        <v>3.45</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33351,10 +33351,10 @@
         <v>0</v>
       </c>
       <c r="AE167" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF167" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG167" t="n">
         <v>0</v>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="R45" t="n">
-        <v>3.59</v>
+        <v>3.63</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R49" t="n">
-        <v>2.65</v>
+        <v>3.23</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="R51" t="n">
-        <v>3.63</v>
+        <v>3.39</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.56</v>
+        <v>2.38</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.67</v>
+        <v>3.45</v>
       </c>
       <c r="R52" t="n">
-        <v>5.75</v>
+        <v>2.65</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.35</v>
+        <v>2.93</v>
       </c>
       <c r="R54" t="n">
-        <v>3.23</v>
+        <v>3.59</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.34</v>
+        <v>1.56</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.38</v>
+        <v>3.67</v>
       </c>
       <c r="R55" t="n">
-        <v>2.83</v>
+        <v>5.75</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.28</v>
+        <v>16.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.07</v>
+        <v>7.39</v>
       </c>
       <c r="R56" t="n">
-        <v>3.21</v>
+        <v>1.12</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>16.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q58" t="n">
-        <v>7.39</v>
+        <v>3.07</v>
       </c>
       <c r="R58" t="n">
-        <v>1.12</v>
+        <v>3.21</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="Q69" t="n">
         <v>3.9</v>
       </c>
       <c r="R69" t="n">
-        <v>4.16</v>
+        <v>5.38</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3</v>
+        <v>1.46</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="R71" t="n">
-        <v>2.16</v>
+        <v>6.36</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.62</v>
+        <v>4.25</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.1</v>
+        <v>3.36</v>
       </c>
       <c r="R72" t="n">
-        <v>5</v>
+        <v>1.82</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="R73" t="n">
-        <v>3.49</v>
+        <v>4.16</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="R76" t="n">
-        <v>1.82</v>
+        <v>2.16</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="R79" t="n">
-        <v>6.36</v>
+        <v>4.73</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.29</v>
+        <v>2.74</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.71</v>
+        <v>3.46</v>
       </c>
       <c r="R92" t="n">
-        <v>2.94</v>
+        <v>2.54</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.46</v>
+        <v>3.71</v>
       </c>
       <c r="R94" t="n">
-        <v>2.54</v>
+        <v>2.94</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF114" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="R122" t="n">
-        <v>3.83</v>
+        <v>2.74</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF132" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R135" t="n">
-        <v>3.58</v>
+        <v>4.68</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AF135" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF136" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF137" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>2.42</v>
+        <v>3.08</v>
       </c>
       <c r="Q154" t="n">
-        <v>3</v>
+        <v>4.26</v>
       </c>
       <c r="R154" t="n">
-        <v>3.03</v>
+        <v>2.12</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30796,10 +30796,10 @@
         <v>0</v>
       </c>
       <c r="AG154" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH154" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI154" t="n">
         <v>0</v>
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>3.08</v>
+        <v>1.6</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.26</v>
+        <v>4.58</v>
       </c>
       <c r="R155" t="n">
-        <v>2.12</v>
+        <v>5.3</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30993,10 +30993,10 @@
         <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31584,10 +31584,10 @@
         <v>0</v>
       </c>
       <c r="AG158" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH158" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI158" t="n">
         <v>0</v>
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="R161" t="n">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32175,10 +32175,10 @@
         <v>0</v>
       </c>
       <c r="AG161" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH161" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AI161" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="R162" t="n">
-        <v>1.72</v>
+        <v>3.15</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32372,10 +32372,10 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH162" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="R45" t="n">
-        <v>3.63</v>
+        <v>3.23</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.11</v>
+        <v>2.34</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="R49" t="n">
-        <v>3.23</v>
+        <v>2.83</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="R51" t="n">
-        <v>3.39</v>
+        <v>3.21</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="R52" t="n">
-        <v>2.65</v>
+        <v>3.63</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.38</v>
+        <v>2.93</v>
       </c>
       <c r="R53" t="n">
-        <v>2.83</v>
+        <v>3.59</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11048,10 +11048,10 @@
         <v>2.19</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="R54" t="n">
-        <v>3.59</v>
+        <v>3.39</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>16.3</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="Q69" t="n">
         <v>3.9</v>
       </c>
       <c r="R69" t="n">
-        <v>5.38</v>
+        <v>4.16</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.46</v>
+        <v>4.25</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.6</v>
+        <v>3.36</v>
       </c>
       <c r="R71" t="n">
-        <v>6.36</v>
+        <v>1.82</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>4.25</v>
+        <v>1.46</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.36</v>
+        <v>4.6</v>
       </c>
       <c r="R72" t="n">
-        <v>1.82</v>
+        <v>6.36</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="Q73" t="n">
         <v>3.9</v>
       </c>
       <c r="R73" t="n">
-        <v>4.16</v>
+        <v>4.73</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R76" t="n">
-        <v>2.16</v>
+        <v>5.38</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="Q77" t="n">
         <v>3.8</v>
       </c>
       <c r="R77" t="n">
-        <v>3.19</v>
+        <v>2.16</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.69</v>
+        <v>2.27</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R79" t="n">
-        <v>4.73</v>
+        <v>3.2</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.1</v>
+        <v>5.06</v>
       </c>
       <c r="R81" t="n">
-        <v>5</v>
+        <v>5.89</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.74</v>
+        <v>3.46</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.46</v>
+        <v>3.82</v>
       </c>
       <c r="R92" t="n">
-        <v>2.54</v>
+        <v>2.01</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>3.46</v>
+        <v>2.29</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.82</v>
+        <v>3.71</v>
       </c>
       <c r="R93" t="n">
-        <v>2.01</v>
+        <v>2.94</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.29</v>
+        <v>2.74</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.71</v>
+        <v>3.46</v>
       </c>
       <c r="R94" t="n">
-        <v>2.94</v>
+        <v>2.54</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.74</v>
+        <v>2.08</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="R122" t="n">
-        <v>2.74</v>
+        <v>3.83</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF129" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF130" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF132" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26659,10 +26659,10 @@
         <v>0</v>
       </c>
       <c r="AG133" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH133" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI133" t="n">
         <v>0</v>
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="Q134" t="n">
-        <v>4.78</v>
+        <v>3.8</v>
       </c>
       <c r="R134" t="n">
-        <v>4.78</v>
+        <v>3.58</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,16 +26850,16 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF134" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG134" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH134" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF135" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="R137" t="n">
-        <v>4.08</v>
+        <v>4.68</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AF137" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,22 +30500,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>3.08</v>
+        <v>1.84</v>
       </c>
       <c r="Q154" t="n">
-        <v>4.26</v>
+        <v>3.91</v>
       </c>
       <c r="R154" t="n">
-        <v>2.12</v>
+        <v>4.32</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30790,16 +30790,16 @@
         <v>0</v>
       </c>
       <c r="AE154" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF154" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG154" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH154" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI154" t="n">
         <v>0</v>
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>1.6</v>
+        <v>3.08</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.58</v>
+        <v>4.26</v>
       </c>
       <c r="R155" t="n">
-        <v>5.3</v>
+        <v>2.12</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30993,10 +30993,10 @@
         <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31584,10 +31584,10 @@
         <v>0</v>
       </c>
       <c r="AG158" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH158" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI158" t="n">
         <v>0</v>
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>3.9</v>
+        <v>2.48</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.95</v>
+        <v>4.02</v>
       </c>
       <c r="R161" t="n">
-        <v>1.72</v>
+        <v>2.64</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32175,10 +32175,10 @@
         <v>0</v>
       </c>
       <c r="AG161" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH161" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AI161" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="R162" t="n">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32372,10 +32372,10 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH162" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32569,10 +32569,10 @@
         <v>0</v>
       </c>
       <c r="AG163" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH163" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI163" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>3.3</v>
+        <v>1.92</v>
       </c>
       <c r="Q166" t="n">
         <v>3.6</v>
       </c>
       <c r="R166" t="n">
-        <v>1.9</v>
+        <v>3.45</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33154,10 +33154,10 @@
         <v>0</v>
       </c>
       <c r="AE166" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF166" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>1.92</v>
+        <v>3.3</v>
       </c>
       <c r="Q167" t="n">
         <v>3.6</v>
       </c>
       <c r="R167" t="n">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33351,10 +33351,10 @@
         <v>0</v>
       </c>
       <c r="AE167" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF167" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG167" t="n">
         <v>0</v>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.21</v>
+        <v>1.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.98</v>
+        <v>3.89</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>3.21</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="R6" t="n">
-        <v>3.89</v>
+        <v>1.98</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.56</v>
+        <v>2.19</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.67</v>
+        <v>3.08</v>
       </c>
       <c r="R46" t="n">
-        <v>5.75</v>
+        <v>3.39</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="R47" t="n">
-        <v>2.65</v>
+        <v>3.63</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="R52" t="n">
-        <v>3.63</v>
+        <v>3.23</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11048,10 +11048,10 @@
         <v>2.19</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="R54" t="n">
-        <v>3.39</v>
+        <v>3.59</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>16.3</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="R70" t="n">
-        <v>5</v>
+        <v>4.73</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>4.25</v>
+        <v>1.62</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.36</v>
+        <v>4.1</v>
       </c>
       <c r="R71" t="n">
-        <v>1.82</v>
+        <v>5</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="R72" t="n">
-        <v>6.36</v>
+        <v>5.38</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="Q73" t="n">
         <v>3.9</v>
       </c>
       <c r="R73" t="n">
-        <v>4.73</v>
+        <v>4.16</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.62</v>
+        <v>2.27</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>5.38</v>
+        <v>3.2</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="Q77" t="n">
         <v>3.8</v>
       </c>
       <c r="R77" t="n">
-        <v>2.16</v>
+        <v>3.19</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R78" t="n">
-        <v>3.19</v>
+        <v>3.49</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R80" t="n">
-        <v>3.49</v>
+        <v>2.16</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.29</v>
+        <v>2.74</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.71</v>
+        <v>3.46</v>
       </c>
       <c r="R93" t="n">
-        <v>2.94</v>
+        <v>2.54</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.46</v>
+        <v>3.71</v>
       </c>
       <c r="R94" t="n">
-        <v>2.54</v>
+        <v>2.94</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF114" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="R122" t="n">
-        <v>3.83</v>
+        <v>2.74</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF129" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF130" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF132" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26659,10 +26659,10 @@
         <v>0</v>
       </c>
       <c r="AG133" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH133" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF134" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF135" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF136" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.9</v>
+        <v>4.78</v>
       </c>
       <c r="R137" t="n">
-        <v>4.68</v>
+        <v>4.78</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,16 +27441,16 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH137" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AG137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="n">
-        <v>0</v>
       </c>
       <c r="AI137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,22 +30500,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="R154" t="n">
-        <v>4.32</v>
+        <v>5.3</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30790,16 +30790,16 @@
         <v>0</v>
       </c>
       <c r="AE154" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF154" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG154" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH154" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI154" t="n">
         <v>0</v>
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>3.08</v>
+        <v>1.84</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.26</v>
+        <v>3.91</v>
       </c>
       <c r="R155" t="n">
-        <v>2.12</v>
+        <v>4.32</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30987,16 +30987,16 @@
         <v>0</v>
       </c>
       <c r="AE155" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF155" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG155" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.42</v>
+        <v>3.08</v>
       </c>
       <c r="Q157" t="n">
-        <v>3</v>
+        <v>4.26</v>
       </c>
       <c r="R157" t="n">
-        <v>3.03</v>
+        <v>2.12</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31387,10 +31387,10 @@
         <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH157" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31584,10 +31584,10 @@
         <v>0</v>
       </c>
       <c r="AG158" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH158" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI158" t="n">
         <v>0</v>
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>2.48</v>
+        <v>3.9</v>
       </c>
       <c r="Q161" t="n">
-        <v>4.02</v>
+        <v>3.95</v>
       </c>
       <c r="R161" t="n">
-        <v>2.64</v>
+        <v>1.72</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32175,10 +32175,10 @@
         <v>0</v>
       </c>
       <c r="AG161" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH161" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AI161" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>3.9</v>
+        <v>2.48</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.95</v>
+        <v>4.02</v>
       </c>
       <c r="R162" t="n">
-        <v>1.72</v>
+        <v>2.64</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32372,10 +32372,10 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH162" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32715,13 +32715,13 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q164" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R164" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -32760,10 +32760,10 @@
         <v>0</v>
       </c>
       <c r="AE164" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF164" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AG164" t="n">
         <v>0</v>
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R165" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -32957,10 +32957,10 @@
         <v>0</v>
       </c>
       <c r="AE165" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF165" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AG165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>1.92</v>
+        <v>3.3</v>
       </c>
       <c r="Q166" t="n">
         <v>3.6</v>
       </c>
       <c r="R166" t="n">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33154,10 +33154,10 @@
         <v>0</v>
       </c>
       <c r="AE166" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF166" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>3.3</v>
+        <v>1.92</v>
       </c>
       <c r="Q167" t="n">
         <v>3.6</v>
       </c>
       <c r="R167" t="n">
-        <v>1.9</v>
+        <v>3.45</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33351,10 +33351,10 @@
         <v>0</v>
       </c>
       <c r="AE167" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF167" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG167" t="n">
         <v>0</v>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.79</v>
+        <v>3.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="R5" t="n">
-        <v>3.89</v>
+        <v>1.98</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.21</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="R6" t="n">
-        <v>1.98</v>
+        <v>3.89</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="R47" t="n">
-        <v>3.63</v>
+        <v>3.23</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>16.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q50" t="n">
-        <v>7.39</v>
+        <v>2.95</v>
       </c>
       <c r="R50" t="n">
-        <v>1.12</v>
+        <v>3.63</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="R55" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.56</v>
+        <v>2.28</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.67</v>
+        <v>3.07</v>
       </c>
       <c r="R56" t="n">
-        <v>5.75</v>
+        <v>3.21</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.1</v>
+        <v>5.06</v>
       </c>
       <c r="R71" t="n">
-        <v>5</v>
+        <v>5.89</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="Q72" t="n">
         <v>3.9</v>
       </c>
       <c r="R72" t="n">
-        <v>5.38</v>
+        <v>4.16</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="R73" t="n">
-        <v>4.16</v>
+        <v>6.36</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.46</v>
+        <v>3</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="R74" t="n">
-        <v>6.36</v>
+        <v>2.16</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.27</v>
+        <v>1.62</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="R76" t="n">
-        <v>3.2</v>
+        <v>5.38</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R77" t="n">
-        <v>3.19</v>
+        <v>3.49</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R78" t="n">
-        <v>3.49</v>
+        <v>3.19</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.39</v>
+        <v>1.69</v>
       </c>
       <c r="Q81" t="n">
-        <v>5.06</v>
+        <v>3.9</v>
       </c>
       <c r="R81" t="n">
-        <v>5.89</v>
+        <v>4.73</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.46</v>
+        <v>3.71</v>
       </c>
       <c r="R93" t="n">
-        <v>2.54</v>
+        <v>2.94</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.29</v>
+        <v>2.74</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.71</v>
+        <v>3.46</v>
       </c>
       <c r="R94" t="n">
-        <v>2.94</v>
+        <v>2.54</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="R115" t="n">
-        <v>3.73</v>
+        <v>2.79</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="R125" t="n">
-        <v>3.83</v>
+        <v>2.74</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AG132" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH132" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF134" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF136" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27447,10 +27447,10 @@
         <v>0</v>
       </c>
       <c r="AG137" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH137" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R138" t="n">
-        <v>4.68</v>
+        <v>3.58</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,22 +30500,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>1.6</v>
+        <v>2.42</v>
       </c>
       <c r="Q154" t="n">
-        <v>4.58</v>
+        <v>3</v>
       </c>
       <c r="R154" t="n">
-        <v>5.3</v>
+        <v>3.03</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30796,10 +30796,10 @@
         <v>0</v>
       </c>
       <c r="AG154" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH154" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI154" t="n">
         <v>0</v>
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="Q155" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="R155" t="n">
-        <v>4.32</v>
+        <v>5.3</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30987,16 +30987,16 @@
         <v>0</v>
       </c>
       <c r="AE155" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF155" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH155" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2.42</v>
+        <v>3.08</v>
       </c>
       <c r="Q156" t="n">
-        <v>3</v>
+        <v>4.26</v>
       </c>
       <c r="R156" t="n">
-        <v>3.03</v>
+        <v>2.12</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31190,10 +31190,10 @@
         <v>0</v>
       </c>
       <c r="AG156" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH156" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI156" t="n">
         <v>0</v>
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>3.08</v>
+        <v>1.84</v>
       </c>
       <c r="Q157" t="n">
-        <v>4.26</v>
+        <v>3.91</v>
       </c>
       <c r="R157" t="n">
-        <v>2.12</v>
+        <v>4.32</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,16 +31381,16 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF157" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG157" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH157" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="Q162" t="n">
-        <v>4.02</v>
+        <v>3.65</v>
       </c>
       <c r="R162" t="n">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32372,10 +32372,10 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH162" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,61 +32518,61 @@
         </is>
       </c>
       <c r="P163" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="R163" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="n">
+        <v>0</v>
+      </c>
+      <c r="V163" t="n">
+        <v>0</v>
+      </c>
+      <c r="W163" t="n">
+        <v>0</v>
+      </c>
+      <c r="X163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="n">
         <v>2</v>
       </c>
-      <c r="Q163" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R163" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="S163" t="n">
-        <v>0</v>
-      </c>
-      <c r="T163" t="n">
-        <v>0</v>
-      </c>
-      <c r="U163" t="n">
-        <v>0</v>
-      </c>
-      <c r="V163" t="n">
-        <v>0</v>
-      </c>
-      <c r="W163" t="n">
-        <v>0</v>
-      </c>
-      <c r="X163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG163" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AH163" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AI163" t="n">
         <v>0</v>
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32715,13 +32715,13 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="Q164" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R164" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -32760,10 +32760,10 @@
         <v>0</v>
       </c>
       <c r="AE164" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF164" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AG164" t="n">
         <v>0</v>
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R165" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -32957,10 +32957,10 @@
         <v>0</v>
       </c>
       <c r="AE165" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF165" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AG165" t="n">
         <v>0</v>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="R47" t="n">
-        <v>3.23</v>
+        <v>3.63</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.45</v>
+        <v>3.07</v>
       </c>
       <c r="R51" t="n">
-        <v>2.65</v>
+        <v>3.21</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.38</v>
+        <v>3.08</v>
       </c>
       <c r="R55" t="n">
-        <v>2.83</v>
+        <v>3.39</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.19</v>
+        <v>16.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.08</v>
+        <v>7.39</v>
       </c>
       <c r="R57" t="n">
-        <v>3.39</v>
+        <v>1.12</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>16.3</v>
+        <v>2.11</v>
       </c>
       <c r="Q58" t="n">
-        <v>7.39</v>
+        <v>3.35</v>
       </c>
       <c r="R58" t="n">
-        <v>1.12</v>
+        <v>3.23</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.39</v>
+        <v>3</v>
       </c>
       <c r="Q71" t="n">
-        <v>5.06</v>
+        <v>3.8</v>
       </c>
       <c r="R71" t="n">
-        <v>5.89</v>
+        <v>2.16</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.77</v>
+        <v>2.27</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R72" t="n">
-        <v>4.16</v>
+        <v>3.2</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="R73" t="n">
-        <v>6.36</v>
+        <v>5.38</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R74" t="n">
-        <v>2.16</v>
+        <v>3.49</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>4.25</v>
+        <v>1.39</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.36</v>
+        <v>5.06</v>
       </c>
       <c r="R75" t="n">
-        <v>1.82</v>
+        <v>5.89</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="Q76" t="n">
         <v>3.9</v>
       </c>
       <c r="R76" t="n">
-        <v>5.38</v>
+        <v>4.73</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.07</v>
+        <v>4.25</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.8</v>
+        <v>3.36</v>
       </c>
       <c r="R78" t="n">
-        <v>3.19</v>
+        <v>1.82</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.27</v>
+        <v>1.46</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R79" t="n">
-        <v>3.2</v>
+        <v>6.36</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.69</v>
+        <v>2.07</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R81" t="n">
-        <v>4.73</v>
+        <v>3.19</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q92" t="n">
         <v>3.46</v>
       </c>
-      <c r="Q92" t="n">
-        <v>3.82</v>
-      </c>
       <c r="R92" t="n">
-        <v>2.01</v>
+        <v>2.54</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.74</v>
+        <v>3.46</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.46</v>
+        <v>3.82</v>
       </c>
       <c r="R94" t="n">
-        <v>2.54</v>
+        <v>2.01</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF113" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF129" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF130" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AG132" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH132" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI132" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R134" t="n">
-        <v>4.68</v>
+        <v>3.58</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AF134" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.89</v>
+        <v>4.78</v>
       </c>
       <c r="R135" t="n">
-        <v>4.08</v>
+        <v>4.78</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,16 +27047,16 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF135" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG135" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH135" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF136" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R138" t="n">
-        <v>3.58</v>
+        <v>4.68</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q152" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30500,22 +30500,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>2.42</v>
+        <v>1.84</v>
       </c>
       <c r="Q154" t="n">
-        <v>3</v>
+        <v>3.91</v>
       </c>
       <c r="R154" t="n">
-        <v>3.03</v>
+        <v>4.32</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30790,10 +30790,10 @@
         <v>0</v>
       </c>
       <c r="AE154" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF154" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG154" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>1.6</v>
+        <v>2.42</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.58</v>
+        <v>3</v>
       </c>
       <c r="R155" t="n">
-        <v>5.3</v>
+        <v>3.03</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30993,10 +30993,10 @@
         <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="R157" t="n">
-        <v>4.32</v>
+        <v>5.3</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,16 +31381,16 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF157" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH157" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="R161" t="n">
-        <v>1.72</v>
+        <v>3.15</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32175,10 +32175,10 @@
         <v>0</v>
       </c>
       <c r="AG161" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH161" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AI161" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="R162" t="n">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32372,10 +32372,10 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH162" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.38</v>
+        <v>1.56</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.45</v>
+        <v>3.67</v>
       </c>
       <c r="R45" t="n">
-        <v>2.65</v>
+        <v>5.75</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="R47" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.56</v>
+        <v>16.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.67</v>
+        <v>7.39</v>
       </c>
       <c r="R49" t="n">
-        <v>5.75</v>
+        <v>1.12</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="R51" t="n">
-        <v>3.21</v>
+        <v>3.63</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.38</v>
+        <v>2.93</v>
       </c>
       <c r="R52" t="n">
-        <v>2.83</v>
+        <v>3.59</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>16.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q57" t="n">
-        <v>7.39</v>
+        <v>3.45</v>
       </c>
       <c r="R57" t="n">
-        <v>1.12</v>
+        <v>2.65</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="Q58" t="n">
         <v>3.35</v>
       </c>
       <c r="R58" t="n">
-        <v>3.23</v>
+        <v>2.97</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="R69" t="n">
-        <v>5</v>
+        <v>4.73</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="Q70" t="n">
         <v>3.9</v>
       </c>
       <c r="R70" t="n">
-        <v>4.16</v>
+        <v>5.38</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="Q71" t="n">
         <v>3.8</v>
       </c>
       <c r="R71" t="n">
-        <v>2.16</v>
+        <v>3.19</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.27</v>
+        <v>4.25</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="R72" t="n">
-        <v>3.2</v>
+        <v>1.82</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.62</v>
+        <v>2.27</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R73" t="n">
-        <v>5.38</v>
+        <v>3.2</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.14</v>
+        <v>1.46</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R74" t="n">
-        <v>3.49</v>
+        <v>6.36</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.39</v>
+        <v>3</v>
       </c>
       <c r="Q75" t="n">
-        <v>5.06</v>
+        <v>3.8</v>
       </c>
       <c r="R75" t="n">
-        <v>5.89</v>
+        <v>2.16</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.69</v>
+        <v>2.14</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>4.73</v>
+        <v>3.49</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.6</v>
+        <v>5.06</v>
       </c>
       <c r="R79" t="n">
-        <v>6.36</v>
+        <v>5.89</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.46</v>
+        <v>3.71</v>
       </c>
       <c r="R92" t="n">
-        <v>2.54</v>
+        <v>2.94</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.29</v>
+        <v>3.46</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.71</v>
+        <v>3.82</v>
       </c>
       <c r="R93" t="n">
-        <v>2.94</v>
+        <v>2.01</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q94" t="n">
         <v>3.46</v>
       </c>
-      <c r="Q94" t="n">
-        <v>3.82</v>
-      </c>
       <c r="R94" t="n">
-        <v>2.01</v>
+        <v>2.54</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="R113" t="n">
-        <v>3.73</v>
+        <v>2.79</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF113" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="R114" t="n">
-        <v>2.79</v>
+        <v>3.73</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF114" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26659,10 +26659,10 @@
         <v>0</v>
       </c>
       <c r="AG133" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH133" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI133" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q135" t="n">
-        <v>4.78</v>
+        <v>3.1</v>
       </c>
       <c r="R135" t="n">
-        <v>4.78</v>
+        <v>3.37</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,16 +27047,16 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF135" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG135" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH135" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="R136" t="n">
-        <v>4.08</v>
+        <v>4.68</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AF136" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF137" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>2.42</v>
+        <v>3.08</v>
       </c>
       <c r="Q155" t="n">
-        <v>3</v>
+        <v>4.26</v>
       </c>
       <c r="R155" t="n">
-        <v>3.03</v>
+        <v>2.12</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30993,10 +30993,10 @@
         <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH155" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>3.08</v>
+        <v>1.6</v>
       </c>
       <c r="Q156" t="n">
-        <v>4.26</v>
+        <v>4.58</v>
       </c>
       <c r="R156" t="n">
-        <v>2.12</v>
+        <v>5.3</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31190,10 +31190,10 @@
         <v>0</v>
       </c>
       <c r="AG156" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AH156" t="n">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="AI156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1.6</v>
+        <v>2.42</v>
       </c>
       <c r="Q157" t="n">
-        <v>4.58</v>
+        <v>3</v>
       </c>
       <c r="R157" t="n">
-        <v>5.3</v>
+        <v>3.03</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31387,10 +31387,10 @@
         <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH157" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>3.9</v>
+        <v>2.48</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.95</v>
+        <v>4.02</v>
       </c>
       <c r="R162" t="n">
-        <v>1.72</v>
+        <v>2.64</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32372,10 +32372,10 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH162" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>2.48</v>
+        <v>3.9</v>
       </c>
       <c r="Q163" t="n">
-        <v>4.02</v>
+        <v>3.95</v>
       </c>
       <c r="R163" t="n">
-        <v>2.64</v>
+        <v>1.72</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32569,10 +32569,10 @@
         <v>0</v>
       </c>
       <c r="AG163" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH163" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AI163" t="n">
         <v>0</v>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.21</v>
+        <v>1.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.98</v>
+        <v>3.89</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>3.21</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="R6" t="n">
-        <v>3.89</v>
+        <v>1.98</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.67</v>
+        <v>3.35</v>
       </c>
       <c r="R45" t="n">
-        <v>5.75</v>
+        <v>3.23</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="R47" t="n">
-        <v>3.65</v>
+        <v>2.65</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.38</v>
+        <v>3.07</v>
       </c>
       <c r="R48" t="n">
-        <v>2.83</v>
+        <v>3.21</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>16.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q49" t="n">
-        <v>7.39</v>
+        <v>3.08</v>
       </c>
       <c r="R49" t="n">
-        <v>1.12</v>
+        <v>3.39</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="R51" t="n">
-        <v>3.63</v>
+        <v>2.97</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="R52" t="n">
-        <v>3.59</v>
+        <v>2.83</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="R53" t="n">
-        <v>3.21</v>
+        <v>3.59</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.38</v>
+        <v>16.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.45</v>
+        <v>7.39</v>
       </c>
       <c r="R57" t="n">
-        <v>2.65</v>
+        <v>1.12</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="R58" t="n">
-        <v>2.97</v>
+        <v>3.63</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="Q69" t="n">
         <v>3.9</v>
       </c>
       <c r="R69" t="n">
-        <v>4.73</v>
+        <v>5.38</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>4.25</v>
+        <v>1.69</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.36</v>
+        <v>3.9</v>
       </c>
       <c r="R72" t="n">
-        <v>1.82</v>
+        <v>4.73</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.27</v>
+        <v>4.25</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="R73" t="n">
-        <v>3.2</v>
+        <v>1.82</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="R74" t="n">
-        <v>6.36</v>
+        <v>5</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R76" t="n">
-        <v>3.49</v>
+        <v>3.19</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.77</v>
+        <v>1.39</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.9</v>
+        <v>5.06</v>
       </c>
       <c r="R77" t="n">
-        <v>4.16</v>
+        <v>5.89</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.39</v>
+        <v>1.77</v>
       </c>
       <c r="Q79" t="n">
-        <v>5.06</v>
+        <v>3.9</v>
       </c>
       <c r="R79" t="n">
-        <v>5.89</v>
+        <v>4.16</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.62</v>
+        <v>2.27</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="R80" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.29</v>
+        <v>2.74</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.71</v>
+        <v>3.46</v>
       </c>
       <c r="R92" t="n">
-        <v>2.94</v>
+        <v>2.54</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>3.46</v>
+        <v>2.29</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.82</v>
+        <v>3.71</v>
       </c>
       <c r="R93" t="n">
-        <v>2.01</v>
+        <v>2.94</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.74</v>
+        <v>3.46</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.46</v>
+        <v>3.82</v>
       </c>
       <c r="R94" t="n">
-        <v>2.54</v>
+        <v>2.01</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="R114" t="n">
-        <v>3.73</v>
+        <v>2.79</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF114" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF129" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF130" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="R134" t="n">
-        <v>3.58</v>
+        <v>3.37</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="AF134" t="n">
-        <v>1.94</v>
+        <v>1.58</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.1</v>
+        <v>3.89</v>
       </c>
       <c r="R135" t="n">
-        <v>3.37</v>
+        <v>4.08</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="AF135" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF136" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="R137" t="n">
-        <v>4.08</v>
+        <v>3.58</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AF137" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,22 +30500,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30790,10 +30790,10 @@
         <v>0</v>
       </c>
       <c r="AE154" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF154" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG154" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>3.08</v>
+        <v>2.42</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.26</v>
+        <v>3</v>
       </c>
       <c r="R155" t="n">
-        <v>2.12</v>
+        <v>3.03</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30993,10 +30993,10 @@
         <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.42</v>
+        <v>1.84</v>
       </c>
       <c r="Q157" t="n">
-        <v>3</v>
+        <v>3.91</v>
       </c>
       <c r="R157" t="n">
-        <v>3.03</v>
+        <v>4.32</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,10 +31381,10 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF157" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31584,10 +31584,10 @@
         <v>0</v>
       </c>
       <c r="AG158" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH158" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI158" t="n">
         <v>0</v>
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="R161" t="n">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32175,10 +32175,10 @@
         <v>0</v>
       </c>
       <c r="AG161" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH161" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AI161" t="n">
         <v>0</v>
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="R163" t="n">
-        <v>1.72</v>
+        <v>3.15</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32569,10 +32569,10 @@
         <v>0</v>
       </c>
       <c r="AG163" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH163" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AI163" t="n">
         <v>0</v>
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32715,13 +32715,13 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q164" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R164" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -32760,10 +32760,10 @@
         <v>0</v>
       </c>
       <c r="AE164" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF164" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AG164" t="n">
         <v>0</v>
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R165" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -32957,10 +32957,10 @@
         <v>0</v>
       </c>
       <c r="AE165" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF165" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AG165" t="n">
         <v>0</v>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.79</v>
+        <v>3.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="R5" t="n">
-        <v>3.89</v>
+        <v>1.98</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.21</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="R6" t="n">
-        <v>1.98</v>
+        <v>3.89</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.35</v>
+        <v>3.07</v>
       </c>
       <c r="R45" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="R47" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.28</v>
+        <v>1.56</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.07</v>
+        <v>3.67</v>
       </c>
       <c r="R48" t="n">
-        <v>3.21</v>
+        <v>5.75</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.19</v>
+        <v>16.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.08</v>
+        <v>7.39</v>
       </c>
       <c r="R49" t="n">
-        <v>3.39</v>
+        <v>1.12</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.22</v>
+        <v>2.93</v>
       </c>
       <c r="R50" t="n">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.38</v>
+        <v>3.08</v>
       </c>
       <c r="R52" t="n">
-        <v>2.83</v>
+        <v>3.39</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.93</v>
+        <v>3.22</v>
       </c>
       <c r="R53" t="n">
-        <v>3.59</v>
+        <v>3.65</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>16.3</v>
+        <v>2.11</v>
       </c>
       <c r="Q57" t="n">
-        <v>7.39</v>
+        <v>3.35</v>
       </c>
       <c r="R57" t="n">
-        <v>1.12</v>
+        <v>3.23</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="R58" t="n">
-        <v>3.63</v>
+        <v>2.65</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.62</v>
+        <v>2.14</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R69" t="n">
-        <v>5.38</v>
+        <v>3.49</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.69</v>
+        <v>2.27</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R72" t="n">
-        <v>4.73</v>
+        <v>3.2</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>4.25</v>
+        <v>1.46</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.36</v>
+        <v>4.6</v>
       </c>
       <c r="R73" t="n">
-        <v>1.82</v>
+        <v>6.36</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="R74" t="n">
-        <v>5</v>
+        <v>4.73</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.39</v>
+        <v>3</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.06</v>
+        <v>3.8</v>
       </c>
       <c r="R77" t="n">
-        <v>5.89</v>
+        <v>2.16</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="R78" t="n">
-        <v>3.49</v>
+        <v>4.16</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="Q79" t="n">
         <v>3.9</v>
       </c>
       <c r="R79" t="n">
-        <v>4.16</v>
+        <v>5.38</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.27</v>
+        <v>1.62</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="R80" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.6</v>
+        <v>5.06</v>
       </c>
       <c r="R81" t="n">
-        <v>6.36</v>
+        <v>5.89</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="R123" t="n">
-        <v>3.83</v>
+        <v>2.74</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF132" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q133" t="n">
-        <v>4.78</v>
+        <v>3.9</v>
       </c>
       <c r="R133" t="n">
-        <v>4.78</v>
+        <v>4.68</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,16 +26653,16 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF133" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG133" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH133" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF134" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="R135" t="n">
-        <v>4.08</v>
+        <v>3.58</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AF135" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.8</v>
+        <v>4.78</v>
       </c>
       <c r="R137" t="n">
-        <v>3.58</v>
+        <v>4.78</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,16 +27441,16 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF137" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG137" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH137" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="R138" t="n">
-        <v>4.68</v>
+        <v>3.37</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,22 +30500,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30796,10 +30796,10 @@
         <v>0</v>
       </c>
       <c r="AG154" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH154" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI154" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>2.42</v>
+        <v>1.6</v>
       </c>
       <c r="Q155" t="n">
-        <v>3</v>
+        <v>4.58</v>
       </c>
       <c r="R155" t="n">
-        <v>3.03</v>
+        <v>5.3</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30993,10 +30993,10 @@
         <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH155" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>1.6</v>
+        <v>2.42</v>
       </c>
       <c r="Q156" t="n">
-        <v>4.58</v>
+        <v>3</v>
       </c>
       <c r="R156" t="n">
-        <v>5.3</v>
+        <v>3.03</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31190,10 +31190,10 @@
         <v>0</v>
       </c>
       <c r="AG156" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH156" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI156" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31584,10 +31584,10 @@
         <v>0</v>
       </c>
       <c r="AG158" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH158" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI158" t="n">
         <v>0</v>
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>3.9</v>
+        <v>2.48</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.95</v>
+        <v>4.02</v>
       </c>
       <c r="R161" t="n">
-        <v>1.72</v>
+        <v>2.64</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32175,10 +32175,10 @@
         <v>0</v>
       </c>
       <c r="AG161" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH161" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AI161" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="Q162" t="n">
-        <v>4.02</v>
+        <v>3.65</v>
       </c>
       <c r="R162" t="n">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32372,10 +32372,10 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH162" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="R163" t="n">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32569,10 +32569,10 @@
         <v>0</v>
       </c>
       <c r="AG163" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH163" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AI163" t="n">
         <v>0</v>
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32715,13 +32715,13 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="Q164" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R164" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -32760,10 +32760,10 @@
         <v>0</v>
       </c>
       <c r="AE164" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF164" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AG164" t="n">
         <v>0</v>
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R165" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -32957,10 +32957,10 @@
         <v>0</v>
       </c>
       <c r="AE165" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF165" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AG165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>3.3</v>
+        <v>1.92</v>
       </c>
       <c r="Q166" t="n">
         <v>3.6</v>
       </c>
       <c r="R166" t="n">
-        <v>1.9</v>
+        <v>3.45</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33154,10 +33154,10 @@
         <v>0</v>
       </c>
       <c r="AE166" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF166" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>1.92</v>
+        <v>3.3</v>
       </c>
       <c r="Q167" t="n">
         <v>3.6</v>
       </c>
       <c r="R167" t="n">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33351,10 +33351,10 @@
         <v>0</v>
       </c>
       <c r="AE167" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF167" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG167" t="n">
         <v>0</v>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.28</v>
+        <v>16.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.07</v>
+        <v>7.39</v>
       </c>
       <c r="R45" t="n">
-        <v>3.21</v>
+        <v>1.12</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.34</v>
+        <v>2.11</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="R47" t="n">
-        <v>2.83</v>
+        <v>3.23</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.56</v>
+        <v>2.27</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.67</v>
+        <v>3.35</v>
       </c>
       <c r="R48" t="n">
-        <v>5.75</v>
+        <v>2.97</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>16.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q49" t="n">
-        <v>7.39</v>
+        <v>3.38</v>
       </c>
       <c r="R49" t="n">
-        <v>1.12</v>
+        <v>2.83</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.35</v>
+        <v>3.07</v>
       </c>
       <c r="R51" t="n">
-        <v>2.97</v>
+        <v>3.21</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.19</v>
+        <v>1.56</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.08</v>
+        <v>3.67</v>
       </c>
       <c r="R52" t="n">
-        <v>3.39</v>
+        <v>5.75</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="R53" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="R57" t="n">
-        <v>3.23</v>
+        <v>3.65</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>4.25</v>
+        <v>1.62</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.36</v>
+        <v>3.9</v>
       </c>
       <c r="R70" t="n">
-        <v>1.82</v>
+        <v>5.38</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.07</v>
+        <v>1.46</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="R71" t="n">
-        <v>3.19</v>
+        <v>6.36</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.27</v>
+        <v>1.39</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.3</v>
+        <v>5.06</v>
       </c>
       <c r="R72" t="n">
-        <v>3.2</v>
+        <v>5.89</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.8</v>
+        <v>3.36</v>
       </c>
       <c r="R77" t="n">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R78" t="n">
-        <v>4.16</v>
+        <v>3.49</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="Q79" t="n">
         <v>3.9</v>
       </c>
       <c r="R79" t="n">
-        <v>5.38</v>
+        <v>4.16</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.62</v>
+        <v>2.27</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="R80" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.39</v>
+        <v>3</v>
       </c>
       <c r="Q81" t="n">
-        <v>5.06</v>
+        <v>3.8</v>
       </c>
       <c r="R81" t="n">
-        <v>5.89</v>
+        <v>2.16</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.74</v>
+        <v>3.46</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.46</v>
+        <v>3.82</v>
       </c>
       <c r="R92" t="n">
-        <v>2.54</v>
+        <v>2.01</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.29</v>
+        <v>2.74</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.71</v>
+        <v>3.46</v>
       </c>
       <c r="R93" t="n">
-        <v>2.94</v>
+        <v>2.54</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>3.46</v>
+        <v>2.29</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.82</v>
+        <v>3.71</v>
       </c>
       <c r="R94" t="n">
-        <v>2.01</v>
+        <v>2.94</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="R114" t="n">
-        <v>2.79</v>
+        <v>3.73</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF114" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.06</v>
+        <v>3.34</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="R115" t="n">
-        <v>3.73</v>
+        <v>1.98</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF115" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF126" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.89</v>
+        <v>3.1</v>
       </c>
       <c r="R132" t="n">
-        <v>4.08</v>
+        <v>3.37</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AF132" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF134" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27250,10 +27250,10 @@
         <v>0</v>
       </c>
       <c r="AG136" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH136" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27447,10 +27447,10 @@
         <v>0</v>
       </c>
       <c r="AG137" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH137" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>3.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="R145" t="n">
-        <v>2.36</v>
+        <v>4.22</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q152" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30796,10 +30796,10 @@
         <v>0</v>
       </c>
       <c r="AG154" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH154" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI154" t="n">
         <v>0</v>
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.58</v>
+        <v>3.91</v>
       </c>
       <c r="R155" t="n">
-        <v>5.3</v>
+        <v>4.32</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30987,16 +30987,16 @@
         <v>0</v>
       </c>
       <c r="AE155" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF155" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG155" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2.42</v>
+        <v>1.6</v>
       </c>
       <c r="Q156" t="n">
-        <v>3</v>
+        <v>4.58</v>
       </c>
       <c r="R156" t="n">
-        <v>3.03</v>
+        <v>5.3</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31190,10 +31190,10 @@
         <v>0</v>
       </c>
       <c r="AG156" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH156" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI156" t="n">
         <v>0</v>
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1.84</v>
+        <v>3.08</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.91</v>
+        <v>4.26</v>
       </c>
       <c r="R157" t="n">
-        <v>4.32</v>
+        <v>2.12</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,16 +31381,16 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF157" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH157" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="Q161" t="n">
-        <v>4.02</v>
+        <v>3.65</v>
       </c>
       <c r="R161" t="n">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32175,10 +32175,10 @@
         <v>0</v>
       </c>
       <c r="AG161" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH161" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AI161" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,61 +32321,61 @@
         </is>
       </c>
       <c r="P162" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="R162" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="n">
+        <v>0</v>
+      </c>
+      <c r="V162" t="n">
+        <v>0</v>
+      </c>
+      <c r="W162" t="n">
+        <v>0</v>
+      </c>
+      <c r="X162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="n">
         <v>2</v>
       </c>
-      <c r="Q162" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R162" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="S162" t="n">
-        <v>0</v>
-      </c>
-      <c r="T162" t="n">
-        <v>0</v>
-      </c>
-      <c r="U162" t="n">
-        <v>0</v>
-      </c>
-      <c r="V162" t="n">
-        <v>0</v>
-      </c>
-      <c r="W162" t="n">
-        <v>0</v>
-      </c>
-      <c r="X162" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y162" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG162" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AH162" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>1.92</v>
+        <v>3.3</v>
       </c>
       <c r="Q166" t="n">
         <v>3.6</v>
       </c>
       <c r="R166" t="n">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33154,10 +33154,10 @@
         <v>0</v>
       </c>
       <c r="AE166" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF166" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>3.3</v>
+        <v>1.92</v>
       </c>
       <c r="Q167" t="n">
         <v>3.6</v>
       </c>
       <c r="R167" t="n">
-        <v>1.9</v>
+        <v>3.45</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33351,10 +33351,10 @@
         <v>0</v>
       </c>
       <c r="AE167" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF167" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG167" t="n">
         <v>0</v>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.83</v>
+        <v>2.66</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>16.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q45" t="n">
-        <v>7.39</v>
+        <v>3.07</v>
       </c>
       <c r="R45" t="n">
-        <v>1.12</v>
+        <v>3.21</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.35</v>
+        <v>2.93</v>
       </c>
       <c r="R47" t="n">
-        <v>3.23</v>
+        <v>3.59</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="Q48" t="n">
         <v>3.35</v>
       </c>
       <c r="R48" t="n">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.34</v>
+        <v>1.29</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.38</v>
+        <v>6.17</v>
       </c>
       <c r="R49" t="n">
-        <v>2.83</v>
+        <v>8</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="R51" t="n">
-        <v>3.21</v>
+        <v>3.63</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.93</v>
+        <v>3.35</v>
       </c>
       <c r="R54" t="n">
-        <v>3.59</v>
+        <v>2.97</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="R55" t="n">
-        <v>3.39</v>
+        <v>3.65</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.07</v>
+        <v>16.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.22</v>
+        <v>7.39</v>
       </c>
       <c r="R57" t="n">
-        <v>3.65</v>
+        <v>1.12</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="R58" t="n">
-        <v>2.65</v>
+        <v>3.39</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.62</v>
+        <v>2.27</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R70" t="n">
-        <v>5.38</v>
+        <v>3.2</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.39</v>
+        <v>1.77</v>
       </c>
       <c r="Q72" t="n">
-        <v>5.06</v>
+        <v>3.9</v>
       </c>
       <c r="R72" t="n">
-        <v>5.89</v>
+        <v>4.16</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="R74" t="n">
-        <v>4.73</v>
+        <v>6.36</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="Q75" t="n">
         <v>3.8</v>
       </c>
       <c r="R75" t="n">
-        <v>3.19</v>
+        <v>2.16</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="R76" t="n">
-        <v>5</v>
+        <v>4.73</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>4.25</v>
+        <v>1.62</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.36</v>
+        <v>3.9</v>
       </c>
       <c r="R77" t="n">
-        <v>1.82</v>
+        <v>5.38</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.14</v>
+        <v>4.25</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="R78" t="n">
-        <v>3.49</v>
+        <v>1.82</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R79" t="n">
-        <v>4.16</v>
+        <v>3.49</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.27</v>
+        <v>2.07</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R80" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="R81" t="n">
-        <v>2.16</v>
+        <v>5</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17388,10 +17388,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17585,10 +17585,10 @@
         <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17782,10 +17782,10 @@
         <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE88" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="R91" t="n">
-        <v>4.65</v>
+        <v>3.8</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18373,16 +18373,16 @@
         <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q92" t="n">
         <v>3.46</v>
       </c>
-      <c r="Q92" t="n">
-        <v>3.82</v>
-      </c>
       <c r="R92" t="n">
-        <v>2.01</v>
+        <v>2.54</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.74</v>
+        <v>3.46</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.46</v>
+        <v>3.82</v>
       </c>
       <c r="R93" t="n">
-        <v>2.54</v>
+        <v>2.01</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.79</v>
+        <v>2.4</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.51</v>
+        <v>2.63</v>
       </c>
       <c r="R108" t="n">
-        <v>4.41</v>
+        <v>3.32</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21722,10 +21722,10 @@
         <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22313,10 +22313,10 @@
         <v>0</v>
       </c>
       <c r="AC111" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD111" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23495,10 +23495,10 @@
         <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD117" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF129" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF130" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF134" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF135" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="Q136" t="n">
-        <v>4.78</v>
+        <v>3.89</v>
       </c>
       <c r="R136" t="n">
-        <v>4.78</v>
+        <v>4.08</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,16 +27244,16 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF136" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG136" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH136" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF137" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27644,10 +27644,10 @@
         <v>0</v>
       </c>
       <c r="AG138" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH138" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>1.84</v>
+        <v>3.08</v>
       </c>
       <c r="Q155" t="n">
-        <v>3.91</v>
+        <v>4.26</v>
       </c>
       <c r="R155" t="n">
-        <v>4.32</v>
+        <v>2.12</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30987,16 +30987,16 @@
         <v>0</v>
       </c>
       <c r="AE155" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF155" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH155" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31387,10 +31387,10 @@
         <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH157" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>2.42</v>
+        <v>1.84</v>
       </c>
       <c r="Q158" t="n">
-        <v>3</v>
+        <v>3.91</v>
       </c>
       <c r="R158" t="n">
-        <v>3.03</v>
+        <v>4.32</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,10 +31578,10 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF158" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG158" t="n">
         <v>0</v>
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="R161" t="n">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32175,10 +32175,10 @@
         <v>0</v>
       </c>
       <c r="AG161" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH161" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AI161" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="Q162" t="n">
-        <v>4.02</v>
+        <v>3.65</v>
       </c>
       <c r="R162" t="n">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32372,10 +32372,10 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH162" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>3.9</v>
+        <v>2.48</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.95</v>
+        <v>4.02</v>
       </c>
       <c r="R163" t="n">
-        <v>1.72</v>
+        <v>2.64</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32569,10 +32569,10 @@
         <v>0</v>
       </c>
       <c r="AG163" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH163" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AI163" t="n">
         <v>0</v>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.28</v>
+        <v>1.56</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.07</v>
+        <v>3.67</v>
       </c>
       <c r="R45" t="n">
-        <v>3.21</v>
+        <v>5.75</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.34</v>
+        <v>16.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.38</v>
+        <v>7.39</v>
       </c>
       <c r="R46" t="n">
-        <v>2.83</v>
+        <v>1.12</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.93</v>
+        <v>3.35</v>
       </c>
       <c r="R47" t="n">
-        <v>3.59</v>
+        <v>3.23</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="R48" t="n">
-        <v>3.23</v>
+        <v>2.65</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.29</v>
+        <v>2.19</v>
       </c>
       <c r="Q49" t="n">
-        <v>6.17</v>
+        <v>3.08</v>
       </c>
       <c r="R49" t="n">
-        <v>8</v>
+        <v>3.39</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.67</v>
+        <v>6.17</v>
       </c>
       <c r="R50" t="n">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.95</v>
+        <v>3.07</v>
       </c>
       <c r="R51" t="n">
-        <v>3.63</v>
+        <v>3.21</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.35</v>
+        <v>2.93</v>
       </c>
       <c r="R54" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="R55" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>16.3</v>
+        <v>2.07</v>
       </c>
       <c r="Q57" t="n">
-        <v>7.39</v>
+        <v>3.22</v>
       </c>
       <c r="R57" t="n">
-        <v>1.12</v>
+        <v>3.65</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.27</v>
+        <v>1.62</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="R70" t="n">
-        <v>3.2</v>
+        <v>5.38</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="R72" t="n">
-        <v>4.16</v>
+        <v>5</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.39</v>
+        <v>1.69</v>
       </c>
       <c r="Q73" t="n">
-        <v>5.06</v>
+        <v>3.9</v>
       </c>
       <c r="R73" t="n">
-        <v>5.89</v>
+        <v>4.73</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.46</v>
+        <v>2.14</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R74" t="n">
-        <v>6.36</v>
+        <v>3.49</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.8</v>
+        <v>3.36</v>
       </c>
       <c r="R75" t="n">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="R76" t="n">
-        <v>4.73</v>
+        <v>6.36</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.9</v>
+        <v>5.06</v>
       </c>
       <c r="R77" t="n">
-        <v>5.38</v>
+        <v>5.89</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R80" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="R81" t="n">
-        <v>5</v>
+        <v>3.19</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="R85" t="n">
-        <v>5.25</v>
+        <v>3.57</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17191,10 +17191,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="R86" t="n">
-        <v>3.83</v>
+        <v>5.25</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17388,10 +17388,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="R87" t="n">
-        <v>3.57</v>
+        <v>3.83</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17585,7 +17585,7 @@
         <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AD87" t="n">
         <v>2.1</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="R90" t="n">
-        <v>4.65</v>
+        <v>3.8</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18176,16 +18176,16 @@
         <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="R91" t="n">
-        <v>3.8</v>
+        <v>4.65</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18373,16 +18373,16 @@
         <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21722,10 +21722,10 @@
         <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22116,10 +22116,10 @@
         <v>0</v>
       </c>
       <c r="AC110" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD110" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE110" t="n">
         <v>0</v>
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="R113" t="n">
-        <v>2.79</v>
+        <v>3.73</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF113" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF114" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF126" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF127" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF129" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF130" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF133" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF134" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF135" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="R136" t="n">
-        <v>4.08</v>
+        <v>3.58</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AF136" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.8</v>
+        <v>4.78</v>
       </c>
       <c r="R137" t="n">
-        <v>3.58</v>
+        <v>4.78</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,16 +27441,16 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF137" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG137" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH137" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27644,10 +27644,10 @@
         <v>0</v>
       </c>
       <c r="AG138" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH138" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI138" t="n">
         <v>0</v>
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>3.08</v>
+        <v>1.6</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.26</v>
+        <v>4.58</v>
       </c>
       <c r="R155" t="n">
-        <v>2.12</v>
+        <v>5.3</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30993,10 +30993,10 @@
         <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>1.6</v>
+        <v>3.08</v>
       </c>
       <c r="Q156" t="n">
-        <v>4.58</v>
+        <v>4.26</v>
       </c>
       <c r="R156" t="n">
-        <v>5.3</v>
+        <v>2.12</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31190,10 +31190,10 @@
         <v>0</v>
       </c>
       <c r="AG156" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AH156" t="n">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="AI156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="R161" t="n">
-        <v>1.72</v>
+        <v>3.15</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32175,10 +32175,10 @@
         <v>0</v>
       </c>
       <c r="AG161" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH161" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AI161" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="R162" t="n">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32372,10 +32372,10 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH162" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI167"/>
+  <dimension ref="A1:BI159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.67</v>
+        <v>3.35</v>
       </c>
       <c r="R45" t="n">
-        <v>5.75</v>
+        <v>3.23</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>16.3</v>
+        <v>2.07</v>
       </c>
       <c r="Q46" t="n">
-        <v>7.39</v>
+        <v>3.22</v>
       </c>
       <c r="R46" t="n">
-        <v>1.12</v>
+        <v>3.65</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.35</v>
+        <v>3.07</v>
       </c>
       <c r="R47" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.38</v>
+        <v>1.56</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.45</v>
+        <v>3.67</v>
       </c>
       <c r="R48" t="n">
-        <v>2.65</v>
+        <v>5.75</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.29</v>
+        <v>16.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>6.17</v>
+        <v>7.39</v>
       </c>
       <c r="R50" t="n">
-        <v>8</v>
+        <v>1.12</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="R51" t="n">
-        <v>3.21</v>
+        <v>3.39</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="R52" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.22</v>
+        <v>2.93</v>
       </c>
       <c r="R57" t="n">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R70" t="n">
-        <v>5.38</v>
+        <v>2.16</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="R71" t="n">
-        <v>2.16</v>
+        <v>5</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="R72" t="n">
-        <v>5</v>
+        <v>4.16</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.69</v>
+        <v>2.27</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R73" t="n">
-        <v>4.73</v>
+        <v>3.2</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R74" t="n">
-        <v>3.49</v>
+        <v>3.19</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>4.25</v>
+        <v>1.69</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.36</v>
+        <v>3.9</v>
       </c>
       <c r="R75" t="n">
-        <v>1.82</v>
+        <v>4.73</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.6</v>
+        <v>5.06</v>
       </c>
       <c r="R76" t="n">
-        <v>6.36</v>
+        <v>5.89</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.06</v>
+        <v>4.6</v>
       </c>
       <c r="R77" t="n">
-        <v>5.89</v>
+        <v>6.36</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.27</v>
+        <v>4.25</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="R80" t="n">
-        <v>3.2</v>
+        <v>1.82</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,133 +16758,133 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI83" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK83" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL83" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AM83" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN83" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO83" t="n">
         <v>0</v>
       </c>
       <c r="AP83" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR83" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS83" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU83" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV83" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW83" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX83" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY83" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ83" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BA83" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BB83" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC83" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD83" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE83" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BF83" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG83" t="n">
         <v>0</v>
@@ -16902,27 +16902,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17090,7 +17090,7 @@
         <v>0</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>46165.5625</v>
+        <v>46165.54166666666</v>
       </c>
     </row>
     <row r="85">
@@ -17099,12 +17099,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17191,10 +17191,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>46165.625</v>
+        <v>46165.5625</v>
       </c>
     </row>
     <row r="86">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="R86" t="n">
-        <v>5.25</v>
+        <v>3.57</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17388,10 +17388,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="R87" t="n">
-        <v>3.83</v>
+        <v>5.25</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17585,10 +17585,10 @@
         <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE87" t="n">
         <v>0</v>
@@ -17887,27 +17887,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.28</v>
+        <v>2.76</v>
       </c>
       <c r="R89" t="n">
-        <v>2.5</v>
+        <v>3.83</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17979,16 +17979,16 @@
         <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18075,7 +18075,7 @@
         <v>0</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>46165.63541666666</v>
+        <v>46165.625</v>
       </c>
     </row>
     <row r="90">
@@ -18084,27 +18084,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.65</v>
+        <v>3.28</v>
       </c>
       <c r="R90" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18176,16 +18176,16 @@
         <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18272,7 +18272,7 @@
         <v>0</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>46165.64583333334</v>
+        <v>46165.63541666666</v>
       </c>
     </row>
     <row r="91">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="R91" t="n">
-        <v>4.65</v>
+        <v>3.8</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18373,16 +18373,16 @@
         <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18478,27 +18478,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.74</v>
+        <v>1.58</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.46</v>
+        <v>4.05</v>
       </c>
       <c r="R92" t="n">
-        <v>2.54</v>
+        <v>4.65</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18666,7 +18666,7 @@
         <v>0</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>46165.65625</v>
+        <v>46165.64583333334</v>
       </c>
     </row>
     <row r="93">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,133 +18728,133 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>3.46</v>
+        <v>1.53</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.82</v>
+        <v>4.33</v>
       </c>
       <c r="R93" t="n">
-        <v>2.01</v>
+        <v>5.75</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ93" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL93" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM93" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN93" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AO93" t="n">
         <v>0</v>
       </c>
       <c r="AP93" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR93" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AS93" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU93" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV93" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AW93" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX93" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY93" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AZ93" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA93" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BB93" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC93" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD93" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE93" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF93" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.29</v>
+        <v>2.74</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.71</v>
+        <v>3.46</v>
       </c>
       <c r="R94" t="n">
-        <v>2.94</v>
+        <v>2.54</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19069,12 +19069,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19257,7 +19257,7 @@
         <v>0</v>
       </c>
       <c r="BI95" s="3" t="n">
-        <v>46165.66666666666</v>
+        <v>46165.65625</v>
       </c>
     </row>
     <row r="96">
@@ -19266,27 +19266,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19454,7 +19454,7 @@
         <v>0</v>
       </c>
       <c r="BI96" s="3" t="n">
-        <v>46165.66666666666</v>
+        <v>46165.65625</v>
       </c>
     </row>
     <row r="97">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21525,10 +21525,10 @@
         <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="Q110" t="n">
-        <v>2.63</v>
+        <v>3.51</v>
       </c>
       <c r="R110" t="n">
-        <v>3.32</v>
+        <v>4.41</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22116,10 +22116,10 @@
         <v>0</v>
       </c>
       <c r="AC110" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD110" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE110" t="n">
         <v>0</v>
@@ -22221,12 +22221,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22313,10 +22313,10 @@
         <v>0</v>
       </c>
       <c r="AC111" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD111" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE111" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="BI111" s="3" t="n">
-        <v>46165.6875</v>
+        <v>46165.66666666666</v>
       </c>
     </row>
     <row r="112">
@@ -22418,12 +22418,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22606,7 +22606,7 @@
         <v>0</v>
       </c>
       <c r="BI112" s="3" t="n">
-        <v>46165.70833333334</v>
+        <v>46165.66666666666</v>
       </c>
     </row>
     <row r="113">
@@ -22615,12 +22615,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="R113" t="n">
-        <v>3.73</v>
+        <v>4.6</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22707,16 +22707,16 @@
         <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD113" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE113" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF113" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22803,7 +22803,7 @@
         <v>0</v>
       </c>
       <c r="BI113" s="3" t="n">
-        <v>46165.70833333334</v>
+        <v>46165.6875</v>
       </c>
     </row>
     <row r="114">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="R115" t="n">
-        <v>2.79</v>
+        <v>3.73</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23206,12 +23206,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="R116" t="n">
-        <v>3.17</v>
+        <v>2.79</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23394,7 +23394,7 @@
         <v>0</v>
       </c>
       <c r="BI116" s="3" t="n">
-        <v>46165.72916666666</v>
+        <v>46165.70833333334</v>
       </c>
     </row>
     <row r="117">
@@ -23403,12 +23403,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.19</v>
+        <v>3.34</v>
       </c>
       <c r="Q117" t="n">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="R117" t="n">
-        <v>3.63</v>
+        <v>1.98</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23495,16 +23495,16 @@
         <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF117" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23591,7 +23591,7 @@
         <v>0</v>
       </c>
       <c r="BI117" s="3" t="n">
-        <v>46165.75</v>
+        <v>46165.70833333334</v>
       </c>
     </row>
     <row r="118">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF118" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -23788,7 +23788,7 @@
         <v>0</v>
       </c>
       <c r="BI118" s="3" t="n">
-        <v>46165.76041666666</v>
+        <v>46165.72916666666</v>
       </c>
     </row>
     <row r="119">
@@ -23797,12 +23797,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23889,10 +23889,10 @@
         <v>0</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD119" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="BI119" s="3" t="n">
-        <v>46165.77083333334</v>
+        <v>46165.75</v>
       </c>
     </row>
     <row r="120">
@@ -23994,12 +23994,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24182,7 +24182,7 @@
         <v>0</v>
       </c>
       <c r="BI120" s="3" t="n">
-        <v>46165.77083333334</v>
+        <v>46165.76041666666</v>
       </c>
     </row>
     <row r="121">
@@ -24388,12 +24388,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24576,7 +24576,7 @@
         <v>0</v>
       </c>
       <c r="BI122" s="3" t="n">
-        <v>46165.79166666666</v>
+        <v>46165.77083333334</v>
       </c>
     </row>
     <row r="123">
@@ -24585,12 +24585,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24773,7 +24773,7 @@
         <v>0</v>
       </c>
       <c r="BI123" s="3" t="n">
-        <v>46165.79166666666</v>
+        <v>46165.77083333334</v>
       </c>
     </row>
     <row r="124">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25176,12 +25176,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25364,7 +25364,7 @@
         <v>0</v>
       </c>
       <c r="BI126" s="3" t="n">
-        <v>46165.8125</v>
+        <v>46165.79166666666</v>
       </c>
     </row>
     <row r="127">
@@ -25373,12 +25373,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF127" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25561,7 +25561,7 @@
         <v>0</v>
       </c>
       <c r="BI127" s="3" t="n">
-        <v>46165.8125</v>
+        <v>46165.79166666666</v>
       </c>
     </row>
     <row r="128">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25767,12 +25767,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF129" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25955,7 +25955,7 @@
         <v>0</v>
       </c>
       <c r="BI129" s="3" t="n">
-        <v>46165.83333333334</v>
+        <v>46165.8125</v>
       </c>
     </row>
     <row r="130">
@@ -25964,12 +25964,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF130" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26152,7 +26152,7 @@
         <v>0</v>
       </c>
       <c r="BI130" s="3" t="n">
-        <v>46165.83333333334</v>
+        <v>46165.8125</v>
       </c>
     </row>
     <row r="131">
@@ -26358,12 +26358,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF132" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26546,7 +26546,7 @@
         <v>0</v>
       </c>
       <c r="BI132" s="3" t="n">
-        <v>46165.85416666666</v>
+        <v>46165.83333333334</v>
       </c>
     </row>
     <row r="133">
@@ -26555,7 +26555,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF133" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26743,7 +26743,7 @@
         <v>0</v>
       </c>
       <c r="BI133" s="3" t="n">
-        <v>46165.85416666666</v>
+        <v>46165.83333333334</v>
       </c>
     </row>
     <row r="134">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="R134" t="n">
-        <v>4.08</v>
+        <v>4.68</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AF134" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R135" t="n">
-        <v>4.68</v>
+        <v>3.58</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AF135" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF136" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27737,12 +27737,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27925,7 +27925,7 @@
         <v>0</v>
       </c>
       <c r="BI139" s="3" t="n">
-        <v>46165.875</v>
+        <v>46165.85416666666</v>
       </c>
     </row>
     <row r="140">
@@ -27934,12 +27934,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="R140" t="n">
-        <v>4.22</v>
+        <v>3.37</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF140" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28122,7 +28122,7 @@
         <v>0</v>
       </c>
       <c r="BI140" s="3" t="n">
-        <v>46165.875</v>
+        <v>46165.85416666666</v>
       </c>
     </row>
     <row r="141">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29116,27 +29116,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF146" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29304,7 +29304,7 @@
         <v>0</v>
       </c>
       <c r="BI146" s="3" t="n">
-        <v>46165.875</v>
+        <v>46165.89583333334</v>
       </c>
     </row>
     <row r="147">
@@ -29313,27 +29313,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29501,7 +29501,7 @@
         <v>0</v>
       </c>
       <c r="BI147" s="3" t="n">
-        <v>46165.875</v>
+        <v>46165.89583333334</v>
       </c>
     </row>
     <row r="148">
@@ -29510,27 +29510,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29614,10 +29614,10 @@
         <v>0</v>
       </c>
       <c r="AG148" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH148" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI148" t="n">
         <v>0</v>
@@ -29698,7 +29698,7 @@
         <v>0</v>
       </c>
       <c r="BI148" s="3" t="n">
-        <v>46165.875</v>
+        <v>46165.89583333334</v>
       </c>
     </row>
     <row r="149">
@@ -29707,12 +29707,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29811,10 +29811,10 @@
         <v>0</v>
       </c>
       <c r="AG149" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH149" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI149" t="n">
         <v>0</v>
@@ -29895,7 +29895,7 @@
         <v>0</v>
       </c>
       <c r="BI149" s="3" t="n">
-        <v>46165.875</v>
+        <v>46165.89583333334</v>
       </c>
     </row>
     <row r="150">
@@ -29904,12 +29904,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>3.01</v>
+        <v>2.42</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R150" t="n">
-        <v>2.36</v>
+        <v>3.03</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30092,7 +30092,7 @@
         <v>0</v>
       </c>
       <c r="BI150" s="3" t="n">
-        <v>46165.875</v>
+        <v>46165.89583333334</v>
       </c>
     </row>
     <row r="151">
@@ -30101,27 +30101,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30289,7 +30289,7 @@
         <v>0</v>
       </c>
       <c r="BI151" s="3" t="n">
-        <v>46165.875</v>
+        <v>46165.90625</v>
       </c>
     </row>
     <row r="152">
@@ -30298,27 +30298,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30486,7 +30486,7 @@
         <v>0</v>
       </c>
       <c r="BI152" s="3" t="n">
-        <v>46165.875</v>
+        <v>46165.91666666666</v>
       </c>
     </row>
     <row r="153">
@@ -30495,27 +30495,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30599,10 +30599,10 @@
         <v>0</v>
       </c>
       <c r="AG153" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH153" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI153" t="n">
         <v>0</v>
@@ -30683,7 +30683,7 @@
         <v>0</v>
       </c>
       <c r="BI153" s="3" t="n">
-        <v>46165.875</v>
+        <v>46165.9375</v>
       </c>
     </row>
     <row r="154">
@@ -30692,12 +30692,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30796,10 +30796,10 @@
         <v>0</v>
       </c>
       <c r="AG154" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH154" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI154" t="n">
         <v>0</v>
@@ -30880,7 +30880,7 @@
         <v>0</v>
       </c>
       <c r="BI154" s="3" t="n">
-        <v>46165.89583333334</v>
+        <v>46165.9375</v>
       </c>
     </row>
     <row r="155">
@@ -30889,7 +30889,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>1.6</v>
+        <v>2.48</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.58</v>
+        <v>4.02</v>
       </c>
       <c r="R155" t="n">
-        <v>5.3</v>
+        <v>2.64</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30993,10 +30993,10 @@
         <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31077,7 +31077,7 @@
         <v>0</v>
       </c>
       <c r="BI155" s="3" t="n">
-        <v>46165.89583333334</v>
+        <v>46165.9375</v>
       </c>
     </row>
     <row r="156">
@@ -31086,12 +31086,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="Q156" t="n">
-        <v>4.26</v>
+        <v>3.25</v>
       </c>
       <c r="R156" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31184,16 +31184,16 @@
         <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF156" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG156" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH156" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI156" t="n">
         <v>0</v>
@@ -31274,7 +31274,7 @@
         <v>0</v>
       </c>
       <c r="BI156" s="3" t="n">
-        <v>46165.89583333334</v>
+        <v>46165.95833333334</v>
       </c>
     </row>
     <row r="157">
@@ -31283,7 +31283,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="Q157" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R157" t="n">
-        <v>3.03</v>
+        <v>2.2</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,10 +31381,10 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF157" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG157" t="n">
         <v>0</v>
@@ -31471,7 +31471,7 @@
         <v>0</v>
       </c>
       <c r="BI157" s="3" t="n">
-        <v>46165.89583333334</v>
+        <v>46165.95833333334</v>
       </c>
     </row>
     <row r="158">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.91</v>
+        <v>3.6</v>
       </c>
       <c r="R158" t="n">
-        <v>4.32</v>
+        <v>3.45</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,10 +31578,10 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AF158" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AG158" t="n">
         <v>0</v>
@@ -31668,7 +31668,7 @@
         <v>0</v>
       </c>
       <c r="BI158" s="3" t="n">
-        <v>46165.89583333334</v>
+        <v>46165.97916666666</v>
       </c>
     </row>
     <row r="159">
@@ -31677,12 +31677,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31865,1582 +31865,6 @@
         <v>0</v>
       </c>
       <c r="BI159" s="3" t="n">
-        <v>46165.90625</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>New Mexico United</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Charleston Battery</t>
-        </is>
-      </c>
-      <c r="G160" t="n">
-        <v>0</v>
-      </c>
-      <c r="H160" t="n">
-        <v>0</v>
-      </c>
-      <c r="I160" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" t="n">
-        <v>0</v>
-      </c>
-      <c r="K160" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" t="n">
-        <v>0</v>
-      </c>
-      <c r="M160" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N160" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P160" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
-      <c r="R160" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" t="n">
-        <v>0</v>
-      </c>
-      <c r="T160" t="n">
-        <v>0</v>
-      </c>
-      <c r="U160" t="n">
-        <v>0</v>
-      </c>
-      <c r="V160" t="n">
-        <v>0</v>
-      </c>
-      <c r="W160" t="n">
-        <v>0</v>
-      </c>
-      <c r="X160" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y160" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ160" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA160" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB160" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC160" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD160" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE160" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF160" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG160" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH160" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI160" s="3" t="n">
-        <v>46165.91666666666</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Colorado Rapids</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>FC Dallas</t>
-        </is>
-      </c>
-      <c r="G161" t="n">
-        <v>0</v>
-      </c>
-      <c r="H161" t="n">
-        <v>0</v>
-      </c>
-      <c r="I161" t="n">
-        <v>0</v>
-      </c>
-      <c r="J161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" t="n">
-        <v>0</v>
-      </c>
-      <c r="L161" t="n">
-        <v>0</v>
-      </c>
-      <c r="M161" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N161" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P161" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R161" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="S161" t="n">
-        <v>0</v>
-      </c>
-      <c r="T161" t="n">
-        <v>0</v>
-      </c>
-      <c r="U161" t="n">
-        <v>0</v>
-      </c>
-      <c r="V161" t="n">
-        <v>0</v>
-      </c>
-      <c r="W161" t="n">
-        <v>0</v>
-      </c>
-      <c r="X161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG161" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH161" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI161" s="3" t="n">
-        <v>46165.9375</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="G162" t="n">
-        <v>0</v>
-      </c>
-      <c r="H162" t="n">
-        <v>0</v>
-      </c>
-      <c r="I162" t="n">
-        <v>0</v>
-      </c>
-      <c r="J162" t="n">
-        <v>0</v>
-      </c>
-      <c r="K162" t="n">
-        <v>0</v>
-      </c>
-      <c r="L162" t="n">
-        <v>0</v>
-      </c>
-      <c r="M162" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N162" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P162" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q162" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R162" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S162" t="n">
-        <v>0</v>
-      </c>
-      <c r="T162" t="n">
-        <v>0</v>
-      </c>
-      <c r="U162" t="n">
-        <v>0</v>
-      </c>
-      <c r="V162" t="n">
-        <v>0</v>
-      </c>
-      <c r="W162" t="n">
-        <v>0</v>
-      </c>
-      <c r="X162" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y162" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG162" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH162" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AI162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI162" s="3" t="n">
-        <v>46165.9375</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>SJ Earthquakes</t>
-        </is>
-      </c>
-      <c r="G163" t="n">
-        <v>0</v>
-      </c>
-      <c r="H163" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163" t="n">
-        <v>0</v>
-      </c>
-      <c r="J163" t="n">
-        <v>0</v>
-      </c>
-      <c r="K163" t="n">
-        <v>0</v>
-      </c>
-      <c r="L163" t="n">
-        <v>0</v>
-      </c>
-      <c r="M163" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N163" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P163" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q163" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="R163" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="S163" t="n">
-        <v>0</v>
-      </c>
-      <c r="T163" t="n">
-        <v>0</v>
-      </c>
-      <c r="U163" t="n">
-        <v>0</v>
-      </c>
-      <c r="V163" t="n">
-        <v>0</v>
-      </c>
-      <c r="W163" t="n">
-        <v>0</v>
-      </c>
-      <c r="X163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG163" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH163" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI163" s="3" t="n">
-        <v>46165.9375</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Orange County SC</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Oakland Roots</t>
-        </is>
-      </c>
-      <c r="G164" t="n">
-        <v>0</v>
-      </c>
-      <c r="H164" t="n">
-        <v>0</v>
-      </c>
-      <c r="I164" t="n">
-        <v>0</v>
-      </c>
-      <c r="J164" t="n">
-        <v>0</v>
-      </c>
-      <c r="K164" t="n">
-        <v>0</v>
-      </c>
-      <c r="L164" t="n">
-        <v>0</v>
-      </c>
-      <c r="M164" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N164" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P164" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q164" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R164" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S164" t="n">
-        <v>0</v>
-      </c>
-      <c r="T164" t="n">
-        <v>0</v>
-      </c>
-      <c r="U164" t="n">
-        <v>0</v>
-      </c>
-      <c r="V164" t="n">
-        <v>0</v>
-      </c>
-      <c r="W164" t="n">
-        <v>0</v>
-      </c>
-      <c r="X164" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y164" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE164" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF164" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ164" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA164" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB164" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC164" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD164" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE164" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF164" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG164" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH164" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI164" s="3" t="n">
-        <v>46165.95833333334</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Monterey Bay</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Birmingham Legion</t>
-        </is>
-      </c>
-      <c r="G165" t="n">
-        <v>0</v>
-      </c>
-      <c r="H165" t="n">
-        <v>0</v>
-      </c>
-      <c r="I165" t="n">
-        <v>0</v>
-      </c>
-      <c r="J165" t="n">
-        <v>0</v>
-      </c>
-      <c r="K165" t="n">
-        <v>0</v>
-      </c>
-      <c r="L165" t="n">
-        <v>0</v>
-      </c>
-      <c r="M165" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N165" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P165" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q165" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R165" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S165" t="n">
-        <v>0</v>
-      </c>
-      <c r="T165" t="n">
-        <v>0</v>
-      </c>
-      <c r="U165" t="n">
-        <v>0</v>
-      </c>
-      <c r="V165" t="n">
-        <v>0</v>
-      </c>
-      <c r="W165" t="n">
-        <v>0</v>
-      </c>
-      <c r="X165" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y165" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE165" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF165" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ165" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA165" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB165" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC165" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD165" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE165" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF165" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG165" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH165" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI165" s="3" t="n">
-        <v>46165.95833333334</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Las Vegas Lights</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Colorado Springs</t>
-        </is>
-      </c>
-      <c r="G166" t="n">
-        <v>0</v>
-      </c>
-      <c r="H166" t="n">
-        <v>0</v>
-      </c>
-      <c r="I166" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" t="n">
-        <v>0</v>
-      </c>
-      <c r="K166" t="n">
-        <v>0</v>
-      </c>
-      <c r="L166" t="n">
-        <v>0</v>
-      </c>
-      <c r="M166" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N166" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P166" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R166" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S166" t="n">
-        <v>0</v>
-      </c>
-      <c r="T166" t="n">
-        <v>0</v>
-      </c>
-      <c r="U166" t="n">
-        <v>0</v>
-      </c>
-      <c r="V166" t="n">
-        <v>0</v>
-      </c>
-      <c r="W166" t="n">
-        <v>0</v>
-      </c>
-      <c r="X166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ166" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA166" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB166" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC166" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD166" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE166" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF166" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG166" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH166" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI166" s="3" t="n">
-        <v>46165.97916666666</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>LA Galaxy</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Houston Dynamo</t>
-        </is>
-      </c>
-      <c r="G167" t="n">
-        <v>0</v>
-      </c>
-      <c r="H167" t="n">
-        <v>0</v>
-      </c>
-      <c r="I167" t="n">
-        <v>0</v>
-      </c>
-      <c r="J167" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" t="n">
-        <v>0</v>
-      </c>
-      <c r="L167" t="n">
-        <v>0</v>
-      </c>
-      <c r="M167" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N167" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P167" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q167" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R167" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="S167" t="n">
-        <v>0</v>
-      </c>
-      <c r="T167" t="n">
-        <v>0</v>
-      </c>
-      <c r="U167" t="n">
-        <v>0</v>
-      </c>
-      <c r="V167" t="n">
-        <v>0</v>
-      </c>
-      <c r="W167" t="n">
-        <v>0</v>
-      </c>
-      <c r="X167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE167" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF167" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ167" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA167" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB167" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC167" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD167" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE167" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF167" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG167" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH167" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI167" s="3" t="n">
         <v>46165.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-05-23.xlsx
+++ b/jogos_2026-05-23.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r